--- a/workspaces/btc_daily_14days/stoch/stoch_14.xlsx
+++ b/workspaces/btc_daily_14days/stoch/stoch_14.xlsx
@@ -575,46 +575,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>14.17322834645668</v>
+        <v>14.12727378163933</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>14.94630706616946</v>
+        <v>14.89820769374588</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.36391697098441</v>
+        <v>13.32066107250319</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11.11479161983601</v>
+        <v>11.07913413299676</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>12.96184657453271</v>
+        <v>12.92040114574937</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.87890530782609</v>
+        <v>10.84426910582116</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11.98886000090199</v>
+        <v>11.95087002284293</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>12.71632551736291</v>
+        <v>12.67601333303129</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>12.65820994955033</v>
+        <v>12.61824977090942</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>9.423119722328437</v>
+        <v>9.393395629775085</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>10.4134643379179</v>
+        <v>10.38070438035967</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4.481649577677281</v>
+        <v>4.468196938774739</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.867238932750759</v>
+        <v>2.858893844222152</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7296595764153651</v>
+        <v>0.7283047254325368</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>102</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.310483248417476</v>
+        <v>7.285170479203607</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.797204352585041</v>
+        <v>0.7938828337960331</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4024183134206538</v>
+        <v>0.4002202157155139</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.400847634262526</v>
+        <v>7.375847511614303</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7.845171575893616</v>
+        <v>7.818774234425774</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.144949011876513</v>
+        <v>8.117758843207071</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>10.02589644258808</v>
+        <v>9.992628161136942</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>7.59614255705781</v>
+        <v>7.570944065714556</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>11.46646455240782</v>
+        <v>11.42856683459981</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.721394461183117</v>
+        <v>4.705895994827145</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>5.500130435615745</v>
+        <v>5.482155531442118</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8.485056532326723</v>
+        <v>8.457646247250693</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.065640730428221</v>
+        <v>8.039605925974264</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.301656257367753</v>
+        <v>9.271722092379761</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>125</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.106561679789841</v>
+        <v>5.087303624236917</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.29618382158759</v>
+        <v>4.280639009681813</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.30359766207846</v>
+        <v>6.280988700055858</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.83445273184649</v>
+        <v>4.816771696137288</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3.495962226970498</v>
+        <v>3.482926642051218</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.595787558336752</v>
+        <v>4.579162266909343</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.909648772765628</v>
+        <v>2.898838677890282</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.8393560498085293</v>
+        <v>0.8358647133847583</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.580290782780637</v>
+        <v>1.574092107284152</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.13394793761902</v>
+        <v>3.122974624037603</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>3.73157924077546</v>
+        <v>3.718603242836025</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.162180589070978</v>
+        <v>2.154853638002812</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.741138569647504</v>
+        <v>1.735275223687047</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.992059065024108</v>
+        <v>1.985447582575041</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.153302265788206</v>
+        <v>-2.158488146757293</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.3169475810660458</v>
+        <v>0.3193940896247867</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.047934923583647</v>
+        <v>6.071000760551598</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.7334150861469055</v>
+        <v>0.7376966535296816</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4863499980867871</v>
+        <v>-0.4865743282266735</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-7.000633151078318</v>
+        <v>-7.023902330604827</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.406030672608466</v>
+        <v>-6.427421689024314</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-6.876037205326014</v>
+        <v>-6.899543503867271</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-5.575303795765173</v>
+        <v>-5.593966024350358</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-5.747331066176294</v>
+        <v>-5.767017195993532</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8.000621115363273</v>
+        <v>-8.028237663493641</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.874666532828741</v>
+        <v>-3.88818756573523</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-4.297433448010956</v>
+        <v>-4.312512108045006</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.709471115664577</v>
+        <v>-5.729620910575598</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>120</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.006561679790401342</v>
+        <v>0.004412147431096969</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.438923778850544</v>
+        <v>-2.431981630736892</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.834395399350491</v>
+        <v>-2.827306841873217</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.704816634817746</v>
+        <v>-2.697393457533025</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.09253455172493119</v>
+        <v>0.09078472984289476</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.113419873586672</v>
+        <v>-2.106668459825656</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.033689021958615</v>
+        <v>-3.023658648291892</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.667953586910983</v>
+        <v>-2.658645553189473</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.894343296485914</v>
+        <v>-1.888114031891384</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.5943832728371206</v>
+        <v>0.5925625022312104</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.224661555670835</v>
+        <v>1.220984933544017</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.248282998267285</v>
+        <v>-1.243631515164125</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.51044426414888</v>
+        <v>2.502392916965775</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.433107021929537</v>
+        <v>4.418780915908926</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>140</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3505811773529928</v>
+        <v>-0.3516267891339098</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-6.964118257543383</v>
+        <v>-6.940556650824078</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-3.787431933452886</v>
+        <v>-3.776409885646203</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.08358264270948013</v>
+        <v>-0.08490495766786665</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.09257952539935843</v>
+        <v>0.09069478249463714</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3252739152915893</v>
+        <v>-0.3243585157253506</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.841480217664504</v>
+        <v>-1.834915071633844</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.31048770170289</v>
+        <v>-2.301733430379578</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-8.09984429358903</v>
+        <v>-8.071077819053478</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-6.806192963523642</v>
+        <v>-6.781848593584698</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-8.446606748793073</v>
+        <v>-8.416189976991561</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.115095149585606</v>
+        <v>-4.099895345563731</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-7.405132991447829</v>
+        <v>-7.378559463986441</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-5.720929831322174</v>
+        <v>-5.700266703138723</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>121</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-6.212446584672783</v>
+        <v>-6.191965474422233</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.039504198962497</v>
+        <v>-2.032208579754297</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.261872601186596</v>
+        <v>-3.251904303766693</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.78682835035503</v>
+        <v>-4.770917539571862</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-6.154716689398775</v>
+        <v>-6.133721052371357</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-8.342342053915772</v>
+        <v>-8.311797242075919</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-9.258011857249862</v>
+        <v>-9.223578237243451</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-7.244767088826976</v>
+        <v>-7.217119970357196</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.165997282501607</v>
+        <v>-3.153113485164148</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.848288294230414</v>
+        <v>-4.829209968985161</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.739722650922772</v>
+        <v>-1.73159277059154</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.363969162197868</v>
+        <v>-3.350319700111108</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-5.446086344431166</v>
+        <v>-5.424604328213476</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-5.195265048563847</v>
+        <v>-5.174882995937004</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-5.570361397133055</v>
+        <v>-5.633720578274684</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.875807119618138</v>
+        <v>-4.936306066534549</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-6.81163962353542</v>
+        <v>-6.890272617903911</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.603557990162699</v>
+        <v>-3.644308507196349</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2927214217727823</v>
+        <v>-0.2932755406469312</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.856700907787641</v>
+        <v>3.901322302018563</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.08093556410720737</v>
+        <v>-0.0872498930309149</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.862438021201271</v>
+        <v>-2.904460141941676</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.382082200618825</v>
+        <v>-1.404861191911088</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.549785768294299</v>
+        <v>-4.61251298887737</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.985214622986092</v>
+        <v>-4.041306764514289</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.741082529237083</v>
+        <v>-2.780894909409362</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.913194785775651</v>
+        <v>1.929476250299111</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.474247481239146</v>
+        <v>4.522947582575398</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>128</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.1496883202099752</v>
+        <v>-0.1499811130026529</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1989004955383038</v>
+        <v>-0.1975148718984769</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.284528306765154</v>
+        <v>-5.267539971793319</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.882430580825421</v>
+        <v>1.875570287529136</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.126367709681531</v>
+        <v>2.118451629889506</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-3.053369215103572</v>
+        <v>-3.042844353935557</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.008760020527752488</v>
+        <v>-0.007227489301740775</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.826952253529001</v>
+        <v>-2.815268892164056</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-6.805618948697678</v>
+        <v>-6.781124996270293</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-6.094141725855295</v>
+        <v>-6.071371999109431</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.734154543265582</v>
+        <v>-4.715902296101596</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-7.050830513326758</v>
+        <v>-7.025269138756165</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-5.120670845784915</v>
+        <v>-5.101773749700889</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-6.437283341853195</v>
+        <v>-6.414552417424602</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-7.038892865664522</v>
+        <v>-7.069266696446114</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.864367262880876</v>
+        <v>-4.88714850305935</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.319903675656334</v>
+        <v>2.33016088130578</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1762853591640976</v>
+        <v>0.1782410947965829</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-7.948964747333648</v>
+        <v>-7.982930381439324</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.619079261241374</v>
+        <v>-4.640771388663168</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.983677897839698</v>
+        <v>-7.016983466298122</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-5.177186725806472</v>
+        <v>-5.204001947088067</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.000224054599116</v>
+        <v>-6.030826920742278</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.816118084291965</v>
+        <v>-3.837733298914216</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.346252484538056</v>
+        <v>-4.370005349536534</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.552204099747513</v>
+        <v>-3.572263413564805</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.1714519352156714</v>
+        <v>-0.1757241313802709</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.8365943053789877</v>
+        <v>0.8373559795219592</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>9.045023218251366</v>
+        <v>9.096029297657843</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>10.8560328721472</v>
+        <v>10.91507670557956</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>8.361469026566418</v>
+        <v>8.409461762163488</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.926241413257337</v>
+        <v>5.96152904348974</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>8.818762593347351</v>
+        <v>8.868875795032729</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>6.552706615842467</v>
+        <v>6.587343751925083</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>9.898188301081383</v>
+        <v>9.949828718550627</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.586559199591441</v>
+        <v>2.595005979726466</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.669967900429349</v>
+        <v>1.672842336385038</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.8252844739510365</v>
+        <v>0.8229027523540964</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.335913353422391</v>
+        <v>2.342287359070987</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.369702786473027</v>
+        <v>2.376670516416233</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.6215470951235957</v>
+        <v>-0.6297909910802062</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-4.660182318271808</v>
+        <v>-4.690414486390118</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>158</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.860526927804763</v>
+        <v>-1.855737754920888</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-4.106607831252092</v>
+        <v>-4.09384064662877</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-4.501448416296824</v>
+        <v>-4.488906204089666</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.838980467726735</v>
+        <v>-1.834986346992352</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.646017622397444</v>
+        <v>-3.635906462471809</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.082486118313462</v>
+        <v>-2.075436311485554</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.2662987613569001</v>
+        <v>-0.2641579511164736</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.973176167746573</v>
+        <v>4.961019114627774</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.913248986584755</v>
+        <v>4.901602706745166</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.791835519781159</v>
+        <v>2.787110521887051</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.682125792909055</v>
+        <v>0.6836230203542826</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.621465352809011</v>
+        <v>2.616740354914903</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.3389572868479434</v>
+        <v>-0.3351598256504005</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.08844439933487536</v>
+        <v>-0.08543849337397091</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-6.036745406824323</v>
+        <v>-6.066270393129159</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-7.651538856956179</v>
+        <v>-7.691761267287895</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-8.046376186662663</v>
+        <v>-8.086206634891354</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-10.28311017501156</v>
+        <v>-10.33289639978105</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-7.673089746297876</v>
+        <v>-7.711130212656364</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-5.012999609496312</v>
+        <v>-5.040144980810965</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-9.045363888025392</v>
+        <v>-9.093620041771366</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-7.939713070098314</v>
+        <v>-7.984025870682466</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-9.584065058176975</v>
+        <v>-9.637303752219914</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-11.5646220260324</v>
+        <v>-11.6292045273394</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-6.24068211964844</v>
+        <v>-6.278402296101419</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-11.73499219300454</v>
+        <v>-11.79957469431154</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-8.994709200530629</v>
+        <v>-9.045226130653091</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-11.90493914768653</v>
+        <v>-11.97010797298016</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-8.048993875765362</v>
+        <v>-8.153573328801322</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.55099081213438</v>
+        <v>-5.631206761489821</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-6.687201998497663</v>
+        <v>-6.775905302833777</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-8.044145809903974</v>
+        <v>-8.148077024156052</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.391724479027083</v>
+        <v>-3.438083937572614</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.942793890664539</v>
+        <v>-1.975682021299427</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.506206539881831</v>
+        <v>-3.563626600645094</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.481371942313416</v>
+        <v>-2.529319016259159</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.4287560708857754</v>
+        <v>0.4155739576049839</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.890533237748969</v>
+        <v>-1.938310625919179</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-4.322808740711693</v>
+        <v>-4.398703047981115</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-7.257249126249597</v>
+        <v>-7.37183868762817</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-4.705062108383984</v>
+        <v>-4.784574501580586</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-6.683896693588601</v>
+        <v>-6.790492267048663</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-6.547492374263825</v>
+        <v>-6.599139494445424</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.55546238362448</v>
+        <v>-4.596212881456879</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.95033109022107</v>
+        <v>-4.990769291363399</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-5.723789723163343</v>
+        <v>-5.769095750635493</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-5.763712806905801</v>
+        <v>-5.808691800114843</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.663287888320077</v>
+        <v>-3.695471279176687</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-10.05763937679792</v>
+        <v>-10.13962092342649</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.209602127786937</v>
+        <v>-4.250850599831509</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-9.687544084200148</v>
+        <v>-9.768978332210246</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-10.52772655146876</v>
+        <v>-10.61910351723839</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-11.63438773622318</v>
+        <v>-11.73294775064667</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-11.59845102922836</v>
+        <v>-11.69856459330123</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-15.62820134150122</v>
+        <v>-15.75518284060998</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-14.47595072892796</v>
+        <v>-14.59637059924279</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.077990251218196</v>
+        <v>1.079246472811519</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5335833617458619</v>
+        <v>-0.5476945110976956</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.821309211199392</v>
+        <v>-1.841838677186153</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-4.769720983182253</v>
+        <v>-4.812039979747567</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.839827345236742</v>
+        <v>-0.8517332807658633</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3.921497392891396</v>
+        <v>3.943729126976791</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.73890787172423</v>
+        <v>4.761285398585024</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.660482681872999</v>
+        <v>-4.709001591513974</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.933358879610402</v>
+        <v>-2.971271534504069</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.592169970628845</v>
+        <v>1.584008685873819</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.188090480352258</v>
+        <v>-2.224348242047576</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.152009604476348</v>
+        <v>-2.189965084702145</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.676095513739106</v>
+        <v>-1.709318794745727</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.255680593167497</v>
+        <v>1.243105240233056</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-7.360694957377916</v>
+        <v>-7.426108856443861</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-8.972268570342379</v>
+        <v>-9.05460416024362</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-4.057402763664626</v>
+        <v>-4.09770866718425</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.042193878844536</v>
+        <v>-3.075118797059652</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.465570846129495</v>
+        <v>-4.507380899945346</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.168128908413635</v>
+        <v>-4.207682736784932</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.056586061176446</v>
+        <v>1.052079191144351</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.245717086383209</v>
+        <v>3.254873015396676</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.808487688993964</v>
+        <v>2.812190498958579</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.1963862324024603</v>
+        <v>0.1763510282159615</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>6.195164310962795</v>
+        <v>6.221597703898382</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>5.3455703976365</v>
+        <v>5.363123718386873</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>5.813029025976199</v>
+        <v>5.835726250298912</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.517875270893569</v>
+        <v>2.514019011146829</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>114</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.370631302666119</v>
+        <v>-3.365580552048556</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.035338944018548</v>
+        <v>2.035322061286998</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.745494674858534</v>
+        <v>-2.741161440345572</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.01633740511758219</v>
+        <v>0.01776118217166101</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.399276792410731</v>
+        <v>-1.396598065620893</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.6525511102170185</v>
+        <v>0.6530407094411714</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.188084192228906</v>
+        <v>-1.185052951706389</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.7795440253247747</v>
+        <v>-0.7765589882929049</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.353431545728256</v>
+        <v>-4.346330804299768</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.448800455834132</v>
+        <v>-3.442070024415223</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-8.044194561208691</v>
+        <v>-8.032788261013501</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-7.132004684259449</v>
+        <v>-7.121212121212132</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-6.674345430064314</v>
+        <v>-6.664273749700889</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-4.668367785365277</v>
+        <v>-4.660166452512314</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-7.194293021064674</v>
+        <v>-7.265551123554367</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.968259796421904</v>
+        <v>-2.000345171791423</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.363128503018679</v>
+        <v>-2.394785340840151</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3312271936911841</v>
+        <v>0.3223487747536566</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-4.480698294885258</v>
+        <v>-4.526969361899049</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-7.602059775972826</v>
+        <v>-7.672416850797987</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-7.203662109740677</v>
+        <v>-7.276372736920422</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-8.524541236471649</v>
+        <v>-8.610799762642579</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-7.725673378457529</v>
+        <v>-7.809730683307635</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-8.56473375764471</v>
+        <v>-8.659855868335562</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-7.056986274312294</v>
+        <v>-7.140471261618664</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-9.586034710249336</v>
+        <v>-9.692295000824956</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-7.439453172268571</v>
+        <v>-7.526342715218135</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-8.045769459089342</v>
+        <v>-8.138690348459086</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>130</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.66040783363627</v>
+        <v>3.65954197092838</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.101095062743248</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.115503975613791</v>
+        <v>0.1165562411812431</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.784218646682746</v>
+        <v>1.784049116495865</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.784258970072194</v>
+        <v>2.783563976652268</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.533683707596751</v>
+        <v>-1.53168817928362</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.387648194099711</v>
+        <v>-2.38469360164882</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.318960255629399</v>
+        <v>-1.316370054419764</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-5.228822169355048</v>
+        <v>-5.223523786755912</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-6.079853656669492</v>
+        <v>-6.073648971783925</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.975603484483642</v>
+        <v>-3.970709988409197</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-5.480904569276227</v>
+        <v>-5.474788369525221</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-6.67086187016929</v>
+        <v>-6.664273749700889</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-7.960511060008962</v>
+        <v>-7.953013955886142</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>133</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>9.160697018135807</v>
+        <v>9.15600738301351</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>8.301003104419756</v>
+        <v>8.297325930715814</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>7.154254698575038</v>
+        <v>7.150792942193888</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.773229635693909</v>
+        <v>2.772370120574919</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.482928721373533</v>
+        <v>1.482980421530954</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.03600975683355</v>
+        <v>4.034637548486032</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.951276039561193</v>
+        <v>3.950517770584064</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.979490188955047</v>
+        <v>1.980333242283528</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.927403403972576</v>
+        <v>4.926852153093712</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>8.590504434587672</v>
+        <v>8.588005163554598</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.880987196477534</v>
+        <v>6.879492440740684</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>8.419724450025214</v>
+        <v>8.41763499658235</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.742282986632716</v>
+        <v>5.741741287893099</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.239581380253568</v>
+        <v>5.239582920921258</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>124</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.764626195919064</v>
+        <v>4.762258856718027</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>8.798213873277383</v>
+        <v>8.793487031151976</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.371087102164665</v>
+        <v>4.369003436181387</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.143821055550426</v>
+        <v>-1.141990501305536</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.682242270622595</v>
+        <v>-1.679877282304545</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.191251945810158</v>
+        <v>-2.188348605280666</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-5.501792114695427</v>
+        <v>-5.495812251920327</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-8.396883040110687</v>
+        <v>-8.388330352186514</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-7.651379129359206</v>
+        <v>-7.642878625465585</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-3.660243504896819</v>
+        <v>-3.654294133074167</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-3.058055157259048</v>
+        <v>-3.052595844488415</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-3.83110019967085</v>
+        <v>-3.824664300046315</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-4.251549421736648</v>
+        <v>-4.244918910991217</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.580808462473591</v>
+        <v>-1.57584274000515</v>
       </c>
     </row>
     <row r="28">
@@ -1716,49 +1716,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.0245472913008129</v>
+        <v>0.01589653201463648</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.290671520063178</v>
+        <v>1.287579253037649</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-3.420743949123334</v>
+        <v>-3.454588147734377</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-5.448764197810803</v>
+        <v>-5.499830236948377</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.207059191433565</v>
+        <v>1.202324038982141</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.7850766687175792</v>
+        <v>0.7751282955383729</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.7003429514453785</v>
+        <v>0.6803741154262113</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.05764931517260408</v>
+        <v>-0.09006013245758737</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.1134094019346747</v>
+        <v>-0.1510600186400453</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.956198867773935</v>
+        <v>-1.001185203667895</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-3.318701593444409</v>
+        <v>-3.379851571463739</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.121329235325533</v>
+        <v>-1.171555370640043</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.057634375656043</v>
+        <v>2.031378424212157</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.148558346695296</v>
+        <v>0.1071867130101012</v>
       </c>
     </row>
     <row r="29">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 3.228</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4081~4094</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4081</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.001987416448372414</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 6.526</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3997~4010</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3997</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.2989246044992555</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 9.823</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3895~3908</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3895</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.4975324860236938</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 13.12</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3770~3783</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3770</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.6827060971066103</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 16.42</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3624~3636</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3624</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.6232513015080983</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 19.72</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3504~3516</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3504</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.6447466251019023</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 23.01</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3364~3376</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3364</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.6569454292147157</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 26.31</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3243~3255</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3243</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.4504275675218068</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 29.61</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3115~3125</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3115</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.237438320209975</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 32.91</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2987~2997</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2987</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.2411860679577273</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 36.21</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2856~2865</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2856</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.07200670596803604</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 39.5</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2740~2748</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2740</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.3100322066728509</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 42.8</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2582~2590</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2582</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.2154460422176925</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 46.1</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2456~2463</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2456</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.08471839923785751</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 49.4</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2323~2328</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2323</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.5563898584841809</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 52.69</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2213~2217</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2213</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.9120646116799591</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 55.99</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2102~2105</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2102</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.9032362641130689</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 59.29</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1990~1992</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1990</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1.372023527179586</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 62.59</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1876~1878</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1876</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.659916312377881</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 65.89</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1760~1761</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1760</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>2.248185757018874</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 69.18</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1630~1631</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1630</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>2.135623604989284</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 72.48</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1497~1498</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1497</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>1.511902133728611</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 75.78</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1373~1374</t>
-        </is>
+      <c r="B28" t="n">
+        <v>1373</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>1.218352072803128</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 79.08</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1235~1235</t>
-        </is>
+      <c r="B29" t="n">
+        <v>1235</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>1.352715525943871</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 82.37</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1090~1090</t>
-        </is>
+      <c r="B30" t="n">
+        <v>1090</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>1.543258927496446</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 85.67</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>913~913</t>
-        </is>
+      <c r="B31" t="n">
+        <v>913</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.7376679229444605</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 88.97</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>719~719</t>
-        </is>
+      <c r="B32" t="n">
+        <v>719</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.914072110944403</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 92.27</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>509~509</t>
-        </is>
+      <c r="B33" t="n">
+        <v>509</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.1588210118136004</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 95.57</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>286~286</t>
-        </is>
+      <c r="B34" t="n">
+        <v>286</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-1.094836921608582</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 98.86</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>12.98275215598051</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 3.228</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>1.077990251218594</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 6.526</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>168~168</t>
-        </is>
+      <c r="B7" t="n">
+        <v>168</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>7.625609298837638</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 9.823</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>270~270</t>
-        </is>
+      <c r="B8" t="n">
+        <v>270</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>7.506561679790025</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 13.12</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>395~395</t>
-        </is>
+      <c r="B9" t="n">
+        <v>395</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>6.747068008903952</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 16.42</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>541~542</t>
-        </is>
+      <c r="B10" t="n">
+        <v>541</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>4.333129945472677</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 19.72</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>661~662</t>
-        </is>
+      <c r="B11" t="n">
+        <v>661</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>3.548857752297586</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 23.01</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>801~802</t>
-        </is>
+      <c r="B12" t="n">
+        <v>801</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>2.868157689765091</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 26.31</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>922~923</t>
-        </is>
+      <c r="B13" t="n">
+        <v>922</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1.677742611534335</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 29.61</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1050~1053</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1050</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.7829149561432942</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 32.91</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1178~1181</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1178</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.6818368703065403</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 36.21</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1309~1313</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1309</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.09435225775757061</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 39.5</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1425~1430</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1425</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.6534148266431714</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 42.8</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1583~1588</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1583</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.4032871205960689</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 46.1</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1709~1715</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1709</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.07361324732367791</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 49.4</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1842~1850</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1842</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.6556004823721366</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 52.69</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1952~1961</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1952</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.9891037970075303</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 55.99</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2063~2073</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2063</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.8774228836446127</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 59.29</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2175~2186</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2175</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-1.212560003650047</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 62.59</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2289~2300</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2289</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.319525276731717</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 65.89</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2405~2417</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2405</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.603905841931123</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 69.18</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2535~2547</t>
-        </is>
+      <c r="B26" t="n">
+        <v>2535</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-1.335212957037612</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 72.48</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2668~2680</t>
-        </is>
+      <c r="B27" t="n">
+        <v>2668</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.8143338425980389</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 75.78</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2792~2804</t>
-        </is>
+      <c r="B28" t="n">
+        <v>2792</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.5676180634339403</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 79.08</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2930~2943</t>
-        </is>
+      <c r="B29" t="n">
+        <v>2930</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.5396496691736132</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 82.37</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3075~3088</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3075</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.5180497191737103</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 85.67</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3252~3265</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3252</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.1810340323079842</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 88.97</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3446~3459</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3446</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.1661761056971187</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 92.27</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3656~3669</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3656</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.0004292186289447386</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 95.57</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3879~3892</t>
-        </is>
+      <c r="B34" t="n">
+        <v>3879</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.1016284834899182</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 98.86</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4081~4094</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4081</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.2462473089740129</v>

--- a/workspaces/btc_daily_14days/stoch/stoch_14.xlsx
+++ b/workspaces/btc_daily_14days/stoch/stoch_14.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Stoch-14 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Stoch-14 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>14.12727378163933</v>
+        <v>14.1397659828179</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>14.89820769374588</v>
+        <v>14.91108894727471</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.32066107250319</v>
+        <v>13.33364078438519</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11.07913413299676</v>
+        <v>11.09208689756887</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>12.92040114574937</v>
+        <v>12.93348886737397</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.84426910582116</v>
+        <v>10.85729056312799</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11.95087002284293</v>
+        <v>11.96391789005685</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>12.67601333303129</v>
+        <v>12.68917866544322</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>12.61824977090942</v>
+        <v>12.63143537049871</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>9.393395629775085</v>
+        <v>9.406789264026443</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>10.38070438035967</v>
+        <v>10.3941531769608</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4.468196938774739</v>
+        <v>4.481642818357145</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.858893844222152</v>
+        <v>2.872446562753758</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7283047254325368</v>
+        <v>0.7178750897349317</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>102</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.285170479203607</v>
+        <v>7.29765596811415</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.7938828337960331</v>
+        <v>0.8067521515948499</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4002202157155139</v>
+        <v>0.4131897301946239</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.375847511614303</v>
+        <v>7.388796921284111</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7.818774234425774</v>
+        <v>7.831858188751617</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.117758843207071</v>
+        <v>8.130778105373899</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9.992628161136942</v>
+        <v>10.00567450069292</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>7.570944065714556</v>
+        <v>7.584106863155931</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>11.42856683459981</v>
+        <v>11.44175160435661</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.705895994827145</v>
+        <v>4.719287958594997</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>5.482155531442118</v>
+        <v>5.495603047611716</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8.457646247250693</v>
+        <v>8.471092371887842</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.039605925974264</v>
+        <v>8.053158834850009</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.271722092379761</v>
+        <v>9.261292456680728</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>125</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.087303624236917</v>
+        <v>5.099785305408112</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.280639009681813</v>
+        <v>4.293508880324893</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.280988700055858</v>
+        <v>6.293960523284603</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.816771696137288</v>
+        <v>4.829717831701366</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3.482926642051218</v>
+        <v>3.496006536745959</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.579162266909343</v>
+        <v>4.592178388983726</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.898838677890282</v>
+        <v>2.911880620009136</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.8358647133847583</v>
+        <v>0.8490237637315161</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.574092107284152</v>
+        <v>1.587272808463318</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.122974624037603</v>
+        <v>3.136365427392619</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>3.718603242836025</v>
+        <v>3.732049865234274</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.154853638002812</v>
+        <v>2.168298572873276</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.735275223687047</v>
+        <v>1.748827532388319</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.985447582575041</v>
+        <v>1.975017946877244</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.158488146757293</v>
+        <v>-2.13557245521875</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.3193940896247867</v>
+        <v>0.3273306594734748</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.071000760551598</v>
+        <v>6.037518089876947</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.7376966535296816</v>
+        <v>0.742014893838018</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4865743282266735</v>
+        <v>-0.4730474991554772</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-7.023902330604827</v>
+        <v>-6.964033485788065</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.427421689024314</v>
+        <v>-6.371307257204265</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-6.899543503867271</v>
+        <v>-6.839050499618672</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-5.593966024350358</v>
+        <v>-5.543205682669139</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-5.767017195993532</v>
+        <v>-5.713984411891779</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8.028237663493641</v>
+        <v>-7.959177789060796</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.88818756573523</v>
+        <v>-3.84751421708723</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-4.312512108045006</v>
+        <v>-4.268593782731024</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.729620910575598</v>
+        <v>-5.404573889857758</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>120</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.004412147431096969</v>
+        <v>0.01670325515489424</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.431981630736892</v>
+        <v>-2.418545689456302</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.827306841873217</v>
+        <v>-2.81375711388732</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.697393457533025</v>
+        <v>-2.683839638979038</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.09078472984289476</v>
+        <v>0.1037116656261148</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.106668459825656</v>
+        <v>-2.09309839295662</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.023658648291892</v>
+        <v>-3.009788176449931</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.658645553189473</v>
+        <v>-2.644716204833728</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.888114031891384</v>
+        <v>-1.874418583291906</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.5925625022312104</v>
+        <v>0.6057984293807124</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.220984933544017</v>
+        <v>1.234122796077848</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.243631515164125</v>
+        <v>-1.229800690440207</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.502392916965775</v>
+        <v>2.515273737449299</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.418780915908926</v>
+        <v>4.408351280210773</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>140</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3516267891339098</v>
+        <v>-0.3392480498933281</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-6.940556650824078</v>
+        <v>-6.92574471153943</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-3.776409885646203</v>
+        <v>-3.762537141911608</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.08490495766786665</v>
+        <v>-0.0720811547332687</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.09069478249463714</v>
+        <v>0.1036075718536367</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3243585157253506</v>
+        <v>-0.311276362733814</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.834915071633844</v>
+        <v>-1.821335210000626</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.301733430379578</v>
+        <v>-2.287852255306987</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-8.071077819053478</v>
+        <v>-8.055508785327071</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-6.781848593584698</v>
+        <v>-6.766436176243658</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-8.416189976991561</v>
+        <v>-8.400214537147626</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.099895345563731</v>
+        <v>-4.085186718346279</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-7.378559463986441</v>
+        <v>-7.362794425477155</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-5.700266703138723</v>
+        <v>-5.710696338836875</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>121</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-6.191965474422233</v>
+        <v>-6.177804526329957</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.032208579754297</v>
+        <v>-2.018752060505179</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.251904303766693</v>
+        <v>-3.238123318104549</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.770917539571862</v>
+        <v>-4.756665679772091</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-6.133721052371357</v>
+        <v>-6.118910128351892</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-8.311797242075919</v>
+        <v>-8.29625501995973</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-9.223578237243451</v>
+        <v>-9.207683694170591</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-7.217119970357196</v>
+        <v>-7.201669657147676</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.153113485164148</v>
+        <v>-3.138868132902957</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.829209968985161</v>
+        <v>-4.8142375688955</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.73159277059154</v>
+        <v>-1.71747418874665</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.350319700111108</v>
+        <v>-3.335741017823992</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-5.424604328213476</v>
+        <v>-5.409263891486773</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-5.174882995937004</v>
+        <v>-5.185312631635156</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>128</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-5.633720578274684</v>
+        <v>-6.026160962966642</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.936306066534549</v>
+        <v>-4.921606731892766</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-6.890272617903911</v>
+        <v>-6.874995420948451</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.644308507196349</v>
+        <v>-3.630045466176689</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2932755406469312</v>
+        <v>-0.2799258642225624</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.901322302018563</v>
+        <v>3.913426303489352</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.0872498930309149</v>
+        <v>-0.07378065774834397</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.904460141941676</v>
+        <v>-2.889931414040035</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.404861191911088</v>
+        <v>-1.390813677306561</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.61251298887737</v>
+        <v>-4.59720056297116</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-4.041306764514289</v>
+        <v>-4.026108984604818</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.780894909409362</v>
+        <v>-3.210295278387264</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.929476250299111</v>
+        <v>1.495812429202957</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.522947582575398</v>
+        <v>4.512517946877246</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>128</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.1499811130026529</v>
+        <v>-0.1374588233270302</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1975148718984769</v>
+        <v>-0.1845249631045007</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.267539971793319</v>
+        <v>-5.25289133098579</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.875570287529136</v>
+        <v>1.887818878912185</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.118451629889506</v>
+        <v>2.130731741712545</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-3.042844353935557</v>
+        <v>-3.028786223680115</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.007227489301740775</v>
+        <v>0.005962224982305031</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.815268892164056</v>
+        <v>-2.800945050674073</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-6.781124996270293</v>
+        <v>-6.765497262324075</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-6.071371999109431</v>
+        <v>-6.055703616263031</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.715902296101596</v>
+        <v>-4.700626512126874</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-7.025269138756165</v>
+        <v>-7.011816850036055</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-5.101773749700889</v>
+        <v>-5.088217703349287</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>131</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-7.069266696446114</v>
+        <v>-7.056744406770491</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.88714850305935</v>
+        <v>-4.872370155241619</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.33016088130578</v>
+        <v>2.34245060332745</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1782410947965829</v>
+        <v>0.1911600747471027</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-7.982930381439324</v>
+        <v>-7.967051065691962</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.640771388663168</v>
+        <v>-4.625916431328235</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-7.016983466298122</v>
+        <v>-7.001184569320657</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-5.204001947088067</v>
+        <v>-5.188589376438259</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.030826920742278</v>
+        <v>-6.015091123914367</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.837733298914216</v>
+        <v>-3.822488312612194</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.370005349536534</v>
+        <v>-4.79341000744963</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.572263413564805</v>
+        <v>-3.558811124844695</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.1757241313802709</v>
+        <v>-0.162168085028668</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.8373559795219592</v>
+        <v>0.826926343823807</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>116</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>9.096029297657843</v>
+        <v>9.108551587333466</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>10.91507670557956</v>
+        <v>10.92429346013196</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>8.409461762163488</v>
+        <v>7.95465479554872</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.96152904348974</v>
+        <v>5.972187344659062</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>8.868875795032729</v>
+        <v>8.878715961636253</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>6.587343751925083</v>
+        <v>6.598119157174864</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>9.949828718550627</v>
+        <v>9.959537143088269</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.595005979726466</v>
+        <v>2.607620657734799</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.672842336385038</v>
+        <v>1.685841218896194</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.8229027523540964</v>
+        <v>0.8364542912323785</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.342287359070987</v>
+        <v>2.355744652781205</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.376670516416233</v>
+        <v>2.390122805136343</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.6297909910802062</v>
+        <v>-0.6162349447286033</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-4.690414486390118</v>
+        <v>-4.70084412208827</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>158</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.855737754920888</v>
+        <v>-1.843215465245265</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-4.09384064662877</v>
+        <v>-4.079400713516854</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-4.488906204089666</v>
+        <v>-4.475899072672064</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.834986346992352</v>
+        <v>-1.821562265641127</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.635906462471809</v>
+        <v>-3.621580736553497</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.075436311485554</v>
+        <v>-2.061552484311491</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.2641579511164736</v>
+        <v>-0.2508555817552818</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.961019114627774</v>
+        <v>4.972658478165414</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.901602706745166</v>
+        <v>4.913330876781302</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.787110521887051</v>
+        <v>2.799917155192745</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.6836230203542826</v>
+        <v>0.6970803140645003</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.616740354914903</v>
+        <v>2.630192643635013</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.3351598256504005</v>
+        <v>-0.3216037792987976</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.08543849337397091</v>
+        <v>-0.09586812907212305</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>126</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-6.066270393129159</v>
+        <v>-6.053748103453536</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-7.691761267287895</v>
+        <v>-7.675508792092828</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-8.086206634891354</v>
+        <v>-8.073199503473752</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-10.33289639978105</v>
+        <v>-10.31579589291017</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-7.711130212656364</v>
+        <v>-7.694831761938353</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-5.040144980810965</v>
+        <v>-5.024781625162632</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-9.093620041771366</v>
+        <v>-9.076521864985693</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-7.984025870682466</v>
+        <v>-7.967118286828473</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-9.637303752219914</v>
+        <v>-9.619647631235146</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-11.6292045273394</v>
+        <v>-12.06992865753231</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-11.79957469431154</v>
+        <v>-11.78612240559143</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-9.045226130653091</v>
+        <v>-9.031670084301489</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-11.97010797298016</v>
+        <v>-11.98053760867831</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>133</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-8.153573328801322</v>
+        <v>-8.141051039125699</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.631206761489821</v>
+        <v>-6.029102415303861</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-6.775905302833777</v>
+        <v>-6.762898171416175</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-8.148077024156052</v>
+        <v>-8.131462692115853</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.438083937572614</v>
+        <v>-3.423274119791294</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.975682021299427</v>
+        <v>-2.377194791291096</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.563626600645094</v>
+        <v>-3.548644873167774</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.529319016259159</v>
+        <v>-2.514533210313239</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.4155739576049839</v>
+        <v>0.4292095979840767</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.938310625919179</v>
+        <v>-1.924905498266348</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-4.398703047981115</v>
+        <v>-4.385245754270898</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-7.37183868762817</v>
+        <v>-7.35838639890806</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-4.784574501580586</v>
+        <v>-4.771018455228983</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-6.790492267048663</v>
+        <v>-6.800921902746815</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>110</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-6.599139494445424</v>
+        <v>-6.586617204769802</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.596212881456879</v>
+        <v>-4.583303071880827</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.990769291363399</v>
+        <v>-4.977762159945797</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-5.769095750635493</v>
+        <v>-5.753113927158822</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-5.808691800114843</v>
+        <v>-6.29772580520487</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.695471279176687</v>
+        <v>-3.682428382882321</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-10.13962092342649</v>
+        <v>-10.12146164436733</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.250850599831509</v>
+        <v>-4.235111522026301</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-9.768978332210246</v>
+        <v>-9.750694670451303</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-10.61910351723839</v>
+        <v>-10.60569838958556</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-11.73294775064667</v>
+        <v>-11.71949045693645</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-11.69856459330123</v>
+        <v>-11.68511230458112</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-15.75518284060998</v>
+        <v>-15.74162679425837</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-14.59637059924279</v>
+        <v>-14.60680023494094</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>111</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.079246472811519</v>
+        <v>1.091768762487142</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5476945110976956</v>
+        <v>-0.5347847015216445</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.841838677186153</v>
+        <v>-1.828831545768551</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-4.812039979747567</v>
+        <v>-5.295366743016189</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.8517332807658633</v>
+        <v>-0.838622476390924</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3.943729126976791</v>
+        <v>3.956772023271157</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.761285398585024</v>
+        <v>4.77290056940172</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.709001591513974</v>
+        <v>-4.692776066877236</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.971271534504069</v>
+        <v>-2.955685894074705</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.584008685873819</v>
+        <v>1.59741381352665</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.224348242047576</v>
+        <v>-2.210890948337358</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.189965084702145</v>
+        <v>-2.176512795982035</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.709318794745727</v>
+        <v>-1.695762748394124</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.243105240233056</v>
+        <v>1.232675604534904</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>112</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-7.426108856443861</v>
+        <v>-7.413586566768238</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-9.05460416024362</v>
+        <v>-9.041694350667569</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-4.09770866718425</v>
+        <v>-4.084701535766648</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.075118797059652</v>
+        <v>-3.062139654661188</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.507380899945346</v>
+        <v>-4.494270095570407</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.207682736784932</v>
+        <v>-4.194639840490566</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.052079191144351</v>
+        <v>1.06564532356478</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.254873015396676</v>
+        <v>3.267697628649394</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.812190498958579</v>
+        <v>2.311667344020037</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.1763510282159615</v>
+        <v>0.1897561558687926</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>6.221597703898382</v>
+        <v>6.2350549976086</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>5.363123718386873</v>
+        <v>5.376576007106983</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>5.835726250298912</v>
+        <v>5.849282296650514</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.514019011146829</v>
+        <v>2.503589375448676</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>114</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.365580552048556</v>
+        <v>-3.353058262372933</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.035322061286998</v>
+        <v>2.048231870863049</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.741161440345572</v>
+        <v>-2.728154308927969</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.01776118217166101</v>
+        <v>0.03074032457012521</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.396598065620893</v>
+        <v>-1.383487261245953</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.6530407094411714</v>
+        <v>0.6660836057355368</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.185052951706389</v>
+        <v>-1.170502818971769</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.7765589882929049</v>
+        <v>-0.7619015578354933</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.346330804299768</v>
+        <v>-4.333132065345005</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.442070024415223</v>
+        <v>-3.428664896762392</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-8.032788261013501</v>
+        <v>-8.019330967303283</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-7.121212121212132</v>
+        <v>-7.107759832492022</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-4.660166452512314</v>
+        <v>-4.670596088210466</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>116</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-7.265551123554367</v>
+        <v>-7.253028833878744</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.000345171791423</v>
+        <v>-1.987435362215372</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.394785340840151</v>
+        <v>-2.381778209422549</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3223487747536566</v>
+        <v>0.3353279171521208</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-4.526969361899049</v>
+        <v>-4.513858557524109</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-7.672416850797987</v>
+        <v>-7.659373954503621</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-7.276372736920422</v>
+        <v>-7.750083839438162</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-8.610799762642579</v>
+        <v>-8.59150075487608</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-7.809730683307635</v>
+        <v>-7.796531944352871</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-8.659855868335562</v>
+        <v>-8.646450740682731</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-7.140471261618664</v>
+        <v>-7.127013967908447</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-9.692295000824956</v>
+        <v>-9.678842712104846</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-7.526342715218135</v>
+        <v>-7.512786668866532</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-8.138690348459086</v>
+        <v>-8.149119984157238</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>130</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.65954197092838</v>
+        <v>3.672064260604003</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.101095062743248</v>
+        <v>-4.088185253167197</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.1165562411812431</v>
+        <v>0.1295633725988452</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.784049116495865</v>
+        <v>1.797028258894329</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.783563976652268</v>
+        <v>2.796674781027207</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.53168817928362</v>
+        <v>-1.518645282989254</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.38469360164882</v>
+        <v>-2.371627347348344</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.316370054419764</v>
+        <v>-1.300620649402624</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.210325047801149</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-6.073648971783925</v>
+        <v>-6.060243844131094</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.970709988409197</v>
+        <v>-3.95725269469898</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-5.474788369525221</v>
+        <v>-5.461336080805111</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-7.953013955886142</v>
+        <v>-7.963443591584294</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>133</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>9.15600738301351</v>
+        <v>9.168529672689132</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>8.297325930715814</v>
+        <v>8.310235740291866</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>7.150792942193888</v>
+        <v>7.16380007361149</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.772370120574919</v>
+        <v>2.785349262973384</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.482980421530954</v>
+        <v>1.496091225905893</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.034637548486032</v>
+        <v>4.047680444780397</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.950517770584064</v>
+        <v>3.96358402488454</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.980333242283528</v>
+        <v>1.994332837406226</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.926852153093712</v>
+        <v>4.940050892048475</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>8.588005163554598</v>
+        <v>8.601410291207429</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.879492440740684</v>
+        <v>6.892949734450902</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>8.41763499658235</v>
+        <v>8.431087285302461</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.741741287893099</v>
+        <v>5.755297334244702</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.239582920921258</v>
+        <v>5.229153285223106</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>124</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.762258856718027</v>
+        <v>4.77478114639365</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>8.793487031151976</v>
+        <v>8.806396840728027</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.369003436181387</v>
+        <v>4.382010567598989</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.141990501305536</v>
+        <v>-1.129011358907071</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.679877282304545</v>
+        <v>-1.666766477929606</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.188348605280666</v>
+        <v>-2.175305708986301</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-5.495812251920327</v>
+        <v>-5.482745997619851</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-8.388330352186514</v>
+        <v>-8.366631310082475</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-7.642878625465585</v>
+        <v>-7.629679886510822</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-3.654294133074167</v>
+        <v>-3.640889005421336</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-3.052595844488415</v>
+        <v>-3.039138550778198</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-3.824664300046315</v>
+        <v>-3.811212011326205</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-4.244918910991217</v>
+        <v>-4.231362864639614</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.57584274000515</v>
+        <v>-1.586272375703302</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>138</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.01589653201463648</v>
+        <v>0.02841882169025922</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.287579253037649</v>
+        <v>1.3004890626137</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-3.454588147734377</v>
+        <v>-3.441581016316775</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-5.499830236948377</v>
+        <v>-5.486851094549912</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.202324038982141</v>
+        <v>1.21543484335708</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.7751282955383729</v>
+        <v>0.7881711918327383</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.6803741154262113</v>
+        <v>0.6934403697266873</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.09006013245758737</v>
+        <v>-0.508286418059356</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.1510600186400453</v>
+        <v>-0.1378612796852821</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.001185203667895</v>
+        <v>-0.9877800760150635</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-3.379851571463739</v>
+        <v>-3.366394277753521</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.171555370640043</v>
+        <v>-1.158103081919933</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.031378424212157</v>
+        <v>2.04493447056376</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.1071867130101012</v>
+        <v>0.09675707731194905</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>145</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.07964521676169767</v>
+        <v>-0.06712292708607492</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.515677721998173</v>
+        <v>4.528587531574225</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.6725331533326226</v>
+        <v>0.6855402847502248</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.492441458353916</v>
+        <v>1.50542060075238</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.114945273959712</v>
+        <v>-1.101834469584773</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.127848163830258</v>
+        <v>-0.1148052675358926</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.235693980966595</v>
+        <v>3.248760235267071</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.147820927012518</v>
+        <v>4.161001936307755</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>6.155786558071831</v>
+        <v>6.168985297026595</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>4.616006200629954</v>
+        <v>4.629411328282785</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>6.480218393553756</v>
+        <v>6.493675687263973</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.824946378485393</v>
+        <v>5.838398667205503</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.025381422712904</v>
+        <v>4.038937469064507</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.344068272230572</v>
+        <v>6.33363863653242</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>177</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.698652075270246</v>
+        <v>5.711174364945869</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.522106710893532</v>
+        <v>3.535016520469583</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.997294501472119</v>
+        <v>2.010301632889721</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.952406391141757</v>
+        <v>4.965385533540221</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>8.933759187369091</v>
+        <v>8.94686999174403</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.276398865197805</v>
+        <v>5.289441761492171</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.191665147925342</v>
+        <v>5.204731402225818</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.854425251968763</v>
+        <v>5.867606261264001</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.793425365786398</v>
+        <v>5.806624104741161</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.203187186408186</v>
+        <v>7.216592314061018</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>8.693349116327965</v>
+        <v>8.706806410038183</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>8.162760522260896</v>
+        <v>8.176212810981006</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.482618905666399</v>
+        <v>5.496174952018002</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>5.732340237942566</v>
+        <v>5.721910602244414</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>194</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.08388126741889579</v>
+        <v>0.09640355709451853</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.565091159609295</v>
+        <v>1.578000969185346</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.23207812311577</v>
+        <v>3.245085254533372</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.424186925826369</v>
+        <v>5.437166068224833</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>7.978549215908835</v>
+        <v>7.991660020283774</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>6.214135483521346</v>
+        <v>6.227178379815712</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>7.675793518826445</v>
+        <v>7.688859773126921</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.208610120044945</v>
+        <v>7.221791129340183</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>9.209465903965743</v>
+        <v>9.222664642920506</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.35934071893783</v>
+        <v>8.372745846590661</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9.700979147197543</v>
+        <v>9.714436440907761</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>10.76629013959459</v>
+        <v>10.7797424283147</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>9.830571611123794</v>
+        <v>9.844127657475397</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>6.47204552071976</v>
+        <v>6.461615885021608</v>
       </c>
     </row>
     <row r="32">
@@ -1927,150 +1927,150 @@
         <v>210</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.744656917885266</v>
+        <v>2.757179207560888</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-2.676440504602809</v>
+        <v>-2.663530695026758</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.2620241221339441</v>
+        <v>0.2750312535515462</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.512484650020461</v>
+        <v>-1.499505507621997</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-3.479477293664068</v>
+        <v>-3.466366489289129</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.277273451186495</v>
+        <v>-1.26423055489213</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.5427547363031309</v>
+        <v>0.5558209906036069</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.4006191386688442</v>
+        <v>-0.3874381293736064</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.39552383229168</v>
+        <v>2.408722571246443</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>3.926351028216189</v>
+        <v>3.93975615586902</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.673978656279537</v>
+        <v>4.687435949989755</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.755980861244012</v>
+        <v>3.769433149964122</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>7.145250059822914</v>
+        <v>7.158806106174517</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>7.871161868289704</v>
+        <v>7.860732232591552</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 93.92</t>
+          <t>X ≈ 93.91</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>223</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.766651365888691</v>
+        <v>1.779173655564314</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.087813178933374</v>
+        <v>5.100722988509425</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.347652992516174</v>
+        <v>3.360660123933776</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2.132614645303029</v>
+        <v>2.145593787701493</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.544820022683936</v>
+        <v>-1.531709218308997</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.9947743813994592</v>
+        <v>1.007817277693825</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.703762637221345</v>
+        <v>2.716828891521821</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>6.272453677901723</v>
+        <v>6.285634687196961</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>9.350467244634252</v>
+        <v>9.363665983589016</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>9.397203046153379</v>
+        <v>9.41060817380621</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>6.501866762194553</v>
+        <v>6.51532405590477</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.8815413993606</v>
+        <v>7.89499368808071</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>6.564425801868623</v>
+        <v>6.577981848220226</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.81414713414491</v>
+        <v>6.803717498446758</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 97.22</t>
+          <t>X ≈ 97.21</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>202</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-6.948883864764447</v>
+        <v>-6.936361575088824</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-3.114912923273231</v>
+        <v>-3.10200311369718</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-2.51968261996884</v>
+        <v>-2.506675488551238</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.5808675423416432</v>
+        <v>0.5938466847401074</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.45260317768102</v>
+        <v>-0.4394923733060807</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.6502107449158672</v>
+        <v>-0.6371678486215018</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.245253557613836</v>
+        <v>1.258319811914312</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>2.758268178634303</v>
+        <v>2.771449187929541</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.22202076769954</v>
+        <v>0.2352195066543032</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.3619945925725929</v>
+        <v>0.375399720225424</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.632488793007489</v>
+        <v>2.645946086717707</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>3.656970960253908</v>
+        <v>3.670423248974018</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>3.236716349309006</v>
+        <v>3.250272395660609</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>3.486437681585294</v>
+        <v>3.476008045887141</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Stoch-14 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Stoch-14 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,53 +2210,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 3.228</t>
+          <t>X &gt; 3.229</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4081</v>
+        <v>4082</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.001987416448372414</v>
+        <v>-0.002283551901868464</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1095006492836177</v>
+        <v>0.109168027842955</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.02113597801998424</v>
+        <v>0.02082255810170608</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1158283715949295</v>
+        <v>0.1154923976984819</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1775258498916443</v>
+        <v>0.177171590817025</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1949691509167053</v>
+        <v>0.1946121508943364</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.2704129228654253</v>
+        <v>0.2700368310116659</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.2815671197346816</v>
+        <v>0.2811854844554844</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.332031768799645</v>
+        <v>0.3316372717486402</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.254380403981159</v>
+        <v>0.253999915046677</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.3082774296576432</v>
+        <v>0.3078824149894572</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3320278854908878</v>
+        <v>0.3316270774861678</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.293100086653844</v>
+        <v>0.2927062496264696</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.3117401579245751</v>
+        <v>0.3119116264460828</v>
       </c>
     </row>
     <row r="7">
@@ -2266,101 +2266,101 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3997</v>
+        <v>3998</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2989246044992555</v>
+        <v>-0.2994151579339999</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2012952956087517</v>
+        <v>-0.2018278093837225</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2583636737029593</v>
+        <v>-0.2588864791688863</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1145738510614933</v>
+        <v>-0.1151313986969953</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.09027538224547271</v>
+        <v>-0.09084508032623972</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.02883400049985596</v>
+        <v>-0.0294161098929635</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.02493921848761005</v>
+        <v>0.02434248159701013</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.02108839020830544</v>
+        <v>0.02048727855179777</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.07382753758191996</v>
+        <v>0.07321229918860439</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.06231703671403466</v>
+        <v>0.06169518635375226</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.09659770389858124</v>
+        <v>0.09596477016565075</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.2451031418141625</v>
+        <v>0.2444331499641166</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2391779761620398</v>
+        <v>0.2385046022271027</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.3029857361906068</v>
+        <v>0.3033821289682876</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 9.823</t>
+          <t>X &gt; 9.824</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3895</v>
+        <v>3896</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.4975324860236938</v>
+        <v>-0.4983117839239668</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.2273564430283415</v>
+        <v>-0.2282331369042154</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2756102864682148</v>
+        <v>-0.2764819035413382</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3107286595320815</v>
+        <v>-0.3115894809962967</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2973929845305747</v>
+        <v>-0.2982669831614544</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2421722469846017</v>
+        <v>-0.2430556915041606</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2360888359797073</v>
+        <v>-0.2369757591493382</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.1766228495610491</v>
+        <v>-0.177533562728911</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.223523786755905</v>
+        <v>-0.2244239967885875</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.05928631469227241</v>
+        <v>-0.06024384413100137</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.04443615962117065</v>
+        <v>-0.04540152970589162</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.03003782814162292</v>
+        <v>0.02905346807597198</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.03490489506297223</v>
+        <v>0.03391149860093634</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.06811767243418387</v>
+        <v>0.06885778260620157</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3770</v>
+        <v>3771</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.6827060971066103</v>
+        <v>-0.6838758614011624</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.3768257882773511</v>
+        <v>-0.3781185127073527</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.4930041520691475</v>
+        <v>-0.4942769985700366</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.4807386182744366</v>
+        <v>-0.4820120251721605</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4227351472156471</v>
+        <v>-0.4240384469610845</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.4020308184001848</v>
+        <v>-0.4033326101095653</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3400320559356089</v>
+        <v>-0.3413531252047122</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2101933920990291</v>
+        <v>-0.211561583362041</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.28312643576254</v>
+        <v>-0.2844775901740277</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.164798945286762</v>
+        <v>-0.1662041090316748</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1692053705779699</v>
+        <v>-0.1706153786498135</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.04041362443997798</v>
+        <v>-0.04185760010213357</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.02147343148291014</v>
+        <v>-0.02293403420824802</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.004545725811475165</v>
+        <v>0.005672945551339126</v>
       </c>
     </row>
     <row r="10">
@@ -2425,46 +2425,46 @@
         <v>3624</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.6232513015080983</v>
+        <v>-0.6249908174466441</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.4048743815923928</v>
+        <v>-0.4067335867444939</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.7574480585930559</v>
+        <v>-0.7592256404027395</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.5298256904828875</v>
+        <v>-0.5316621237081733</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.4201632596804288</v>
+        <v>-0.4220504969962491</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1352556415839956</v>
+        <v>-0.137211465317975</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.09478953760477538</v>
+        <v>-0.09676061488353582</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.05930029341921994</v>
+        <v>0.05726867896955667</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.06916877021787826</v>
+        <v>-0.0711682552963282</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.06089748534326134</v>
+        <v>0.05883002576976537</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1474112725692933</v>
+        <v>0.1453114078652078</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.1146015508991809</v>
+        <v>0.1125109216133211</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.151399539482334</v>
+        <v>0.1492822966507106</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.2355579578513414</v>
+        <v>0.2251283221531892</v>
       </c>
     </row>
     <row r="11">
@@ -2477,46 +2477,46 @@
         <v>3504</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.6447466251019023</v>
+        <v>-0.6469666418508098</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3354529004573052</v>
+        <v>-0.3378359119940839</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.686562483823181</v>
+        <v>-0.6888649735025822</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.4555939176387014</v>
+        <v>-0.4579574142810827</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4376614784997273</v>
+        <v>-0.4400560505107052</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.06774150397298229</v>
+        <v>-0.07022903628924837</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.005514199062595537</v>
+        <v>0.003000602978325162</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1523806306318534</v>
+        <v>0.1498024078669289</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.006876124270156936</v>
+        <v>-0.009413107077300253</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.04268977928545326</v>
+        <v>0.04009823112555466</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.110645051303031</v>
+        <v>0.1080233466250462</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.1611163819287498</v>
+        <v>0.1584804973685721</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.07088606765071148</v>
+        <v>0.06825519251376733</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.09229689764389803</v>
+        <v>0.08186726194574589</v>
       </c>
     </row>
     <row r="12">
@@ -2529,46 +2529,46 @@
         <v>3364</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.6569454292147157</v>
+        <v>-0.6597730041795984</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.06056748872979512</v>
+        <v>-0.06366610464083067</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.5579719260778759</v>
+        <v>-0.5609475824272963</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.4710209254852913</v>
+        <v>-0.4740164738342116</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.4596501457230318</v>
+        <v>-0.4626817660668934</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.05706184236616707</v>
+        <v>-0.06019734018275358</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.08210756942450814</v>
+        <v>0.07892420993939453</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2545137960722741</v>
+        <v>0.2512505805317176</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.328732745310603</v>
+        <v>0.3254422421958765</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.3267074285725613</v>
+        <v>0.3233666071754016</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4655073889847401</v>
+        <v>0.462111724665526</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3384474288517367</v>
+        <v>0.3350897156206827</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.3809105546986302</v>
+        <v>0.377514094570472</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.3333667264517359</v>
+        <v>0.3229370907535838</v>
       </c>
     </row>
     <row r="13">
@@ -2581,46 +2581,46 @@
         <v>3243</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.4504275675218068</v>
+        <v>-0.4538890035073209</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.01299667161986662</v>
+        <v>0.009280364881085745</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4574582604286732</v>
+        <v>-0.4610591260545078</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3105869167574156</v>
+        <v>-0.3142259854227092</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2479441390303236</v>
+        <v>-0.2516414848962256</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.2509316770186274</v>
+        <v>0.2470992923343616</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.4293132378200752</v>
+        <v>0.425418060200677</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.5332889073081617</v>
+        <v>0.5293274688324345</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.4586443684642916</v>
+        <v>0.454699582740723</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.5190805414632393</v>
+        <v>0.5150564330479241</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.5474836823269271</v>
+        <v>0.543434541663018</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.476079504893832</v>
+        <v>0.4720525644479423</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5975208848967029</v>
+        <v>0.5934253299429386</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.538885757105156</v>
+        <v>0.5284561214070038</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>3115</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.237438320209975</v>
+        <v>-0.2249160305343523</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2163709093353674</v>
+        <v>0.2118978764018138</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.1931243157234306</v>
+        <v>-0.1975009091214659</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.1735993201037473</v>
+        <v>-0.1779740131798491</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2460814040682351</v>
+        <v>-0.2504792375274363</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1009316770186359</v>
+        <v>0.09644444243777883</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.4505395879802521</v>
+        <v>0.4459308807134974</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.674551147534153</v>
+        <v>0.6698299205202858</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.5352185937381506</v>
+        <v>0.5305344775356033</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.7299453799491502</v>
+        <v>0.7251267044734249</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.7360439318279504</v>
+        <v>0.7312039064663125</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.6099134455136763</v>
+        <v>0.6233657342337864</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.5427888506201342</v>
+        <v>0.5563448969717371</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.3751747093811773</v>
+        <v>0.3647450736830251</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>2987</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.2411860679577273</v>
+        <v>-0.2286637782821046</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2341068919258973</v>
+        <v>0.2288855307228062</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.02432637191532194</v>
+        <v>0.0191345023276881</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.261411074297591</v>
+        <v>-0.2664981143474989</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.3474072254095688</v>
+        <v>-0.3525197481878735</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.2356498999721452</v>
+        <v>0.2303679527367777</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.4701559876762929</v>
+        <v>0.4647845760377791</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.8240981730049839</v>
+        <v>0.8185608198550298</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.8487411848064781</v>
+        <v>0.8431866578844733</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.021397882299155</v>
+        <v>1.01570128802021</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.9696726955289776</v>
+        <v>0.963970660259406</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.9370990400187083</v>
+        <v>0.9505513287388183</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.7846716804966292</v>
+        <v>0.7982277268482321</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.6661305420665258</v>
+        <v>0.6557009063683736</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>2856</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.07200670596803604</v>
+        <v>0.08452899564365879</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.4690104131944821</v>
+        <v>0.4628716983913463</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.08143844626751218</v>
+        <v>-0.08743216757110162</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2815771926979167</v>
+        <v>-0.2874901391274065</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.00282160282567645</v>
+        <v>-0.003253780893395231</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.4593232854102425</v>
+        <v>0.4531176916417152</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.8135787007262465</v>
+        <v>0.8072362420188526</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.100597163107288</v>
+        <v>1.094098871575767</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.164295604213642</v>
+        <v>1.157764525326918</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.244278199084505</v>
+        <v>1.237621049113656</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.214594902778131</v>
+        <v>1.228052196488349</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.143936043316835</v>
+        <v>1.157388332036945</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.8287234491786606</v>
+        <v>0.8422794955302635</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.6582767142280588</v>
+        <v>0.6478470785299066</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>2740</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.3100322066728509</v>
+        <v>-0.2975099169972282</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.02676819059715996</v>
+        <v>0.01997939023005557</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.4409072142156774</v>
+        <v>-0.4279000827980752</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5458838800693684</v>
+        <v>-0.5524983829665402</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3725295965524253</v>
+        <v>-0.3792787772924555</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1998888423023217</v>
+        <v>0.1929643449257128</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4267885539862348</v>
+        <v>0.4197665688348877</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.037330220505893</v>
+        <v>1.030022766760275</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.142765888545071</v>
+        <v>1.135407993774351</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.262117451573822</v>
+        <v>1.254604751272126</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.166853178351133</v>
+        <v>1.18031047206135</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.091747284601674</v>
+        <v>1.105199573321784</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.890470775846552</v>
+        <v>0.9040268221981549</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.8847176555681031</v>
+        <v>0.874288019869951</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>2582</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.2154460422176925</v>
+        <v>-0.2029237525420697</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2789200869107447</v>
+        <v>0.2708322393361868</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.1931985231234705</v>
+        <v>-0.1801913917058684</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.4669999955713635</v>
+        <v>-0.4748407170244136</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.1728341880259805</v>
+        <v>-0.1808730028682746</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.3391225271584304</v>
+        <v>0.3309247086048401</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.4690695562349703</v>
+        <v>0.4608038654240687</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.7972284214078158</v>
+        <v>0.7887615574643689</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.9127518617148596</v>
+        <v>0.9042260357901881</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.168798743165809</v>
+        <v>1.160042644448168</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.196423420397416</v>
+        <v>1.209880714107634</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.9984285761936604</v>
+        <v>1.01188086491377</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.9654706344974144</v>
+        <v>0.9790266808490173</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.9440842982996429</v>
+        <v>0.9336546626014908</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>2456</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.08471839923785751</v>
+        <v>0.09724068891348026</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.6878394071994478</v>
+        <v>0.6785028297107942</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2117359321219539</v>
+        <v>0.224743063539556</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.03914941278792128</v>
+        <v>0.03002913320426615</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.2139024972767061</v>
+        <v>0.2046151093641484</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.6150947201568613</v>
+        <v>0.6056881442948594</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.9596635665561379</v>
+        <v>0.9500966349809161</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.247732509682798</v>
+        <v>1.237963862179726</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.454000643211515</v>
+        <v>1.444131606655503</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.825373829519094</v>
+        <v>1.838778957171925</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.579903892823658</v>
+        <v>1.593361186533876</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.655003662546946</v>
+        <v>1.668455951267056</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.479048725869148</v>
+        <v>1.492604772220751</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.60662022101188</v>
+        <v>1.596190585313728</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>2323</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5563898584841809</v>
+        <v>0.5689121481598036</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.049627242083503</v>
+        <v>1.062537051659554</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.6118032090264336</v>
+        <v>0.6248103404440357</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.5078972027636155</v>
+        <v>0.4973035252695084</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.422991690490214</v>
+        <v>0.4123246519718506</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.7634258895988282</v>
+        <v>0.7764687858931936</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.218637992831539</v>
+        <v>1.207665563342424</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.463982123522783</v>
+        <v>1.452807646356035</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.513454258874738</v>
+        <v>1.502239496088691</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.040858131100364</v>
+        <v>2.054263258753195</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.922200372861134</v>
+        <v>1.935657666571352</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.171822445402427</v>
+        <v>2.185274734122537</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.837663400535874</v>
+        <v>1.851219446887477</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.087384732812161</v>
+        <v>2.076955097114009</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>2213</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.9120646116799591</v>
+        <v>0.9245869013555819</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.330260958120306</v>
+        <v>1.343170767696357</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.8902862524258381</v>
+        <v>0.9032933838434403</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.8199031787572508</v>
+        <v>0.8079885319424065</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.732745501591225</v>
+        <v>0.7458563059661643</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.9850610855162714</v>
+        <v>0.9981039818106368</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.783214802948301</v>
+        <v>1.770794344566127</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.748045205117442</v>
+        <v>1.735532955222752</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.074262024360216</v>
+        <v>2.061581004592711</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.670137743082854</v>
+        <v>2.683542870735685</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.600947003491889</v>
+        <v>2.614404297202107</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.861267802048346</v>
+        <v>2.874720090768456</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.712138360556679</v>
+        <v>2.725694406908282</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.916672164590764</v>
+        <v>2.906242528892612</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>2102</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.9032362641130689</v>
+        <v>0.9157585537886916</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.429429872051422</v>
+        <v>1.442339681627473</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.034561165454832</v>
+        <v>1.047568296872434</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.117308359820058</v>
+        <v>1.130287502218522</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.8164168359592736</v>
+        <v>0.8295276403342129</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.8288231442212606</v>
+        <v>0.841866040515626</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.625952273873288</v>
+        <v>1.6122625696105</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.089021510743549</v>
+        <v>2.074991709482077</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.340700761293569</v>
+        <v>2.326527068223577</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.727492797959265</v>
+        <v>2.740897925612096</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.855755648713043</v>
+        <v>2.86921294242326</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.128007502538019</v>
+        <v>3.141459791258129</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.945621588072655</v>
+        <v>2.959177634424258</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.00504796316531</v>
+        <v>2.994618327467158</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>1990</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.372023527179586</v>
+        <v>1.384545816855208</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.019486058793639</v>
+        <v>2.03239586836969</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.323412532919939</v>
+        <v>1.336419664337541</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.35326405910174</v>
+        <v>1.366243201500204</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.116047663306674</v>
+        <v>1.129158467681613</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.112284781745231</v>
+        <v>1.125327678039596</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.658250658428884</v>
+        <v>1.643026957327642</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.023405747667596</v>
+        <v>2.007864542172157</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.314164655455144</v>
+        <v>2.327363394409907</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.871074646306617</v>
+        <v>2.884479773959448</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.666321321989038</v>
+        <v>2.679778615699256</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.002212017022906</v>
+        <v>3.015664305743016</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.782962431203636</v>
+        <v>2.796518477555239</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.032683763479923</v>
+        <v>3.022254127781771</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1876</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.659916312377881</v>
+        <v>1.672438602053504</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.018523743077104</v>
+        <v>2.031433552653155</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.570406900165281</v>
+        <v>1.583414031582883</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.434419351196631</v>
+        <v>1.447398493595095</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.268735090331063</v>
+        <v>1.281845894706002</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.140191937524897</v>
+        <v>1.153234833819262</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.831031368213225</v>
+        <v>1.813998382966297</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.193552858488225</v>
+        <v>2.17617655464597</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.718906916868825</v>
+        <v>2.732105655823588</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.254709237171383</v>
+        <v>3.268114364824214</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.316480433109668</v>
+        <v>3.329937726819885</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.617388110710962</v>
+        <v>3.630840399431072</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.357048211919576</v>
+        <v>3.370604258271179</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.500159736093522</v>
+        <v>3.48973010039537</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1760</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.248185757018874</v>
+        <v>2.260708046694496</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.283403739738887</v>
+        <v>2.296313549314938</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.831749116049735</v>
+        <v>1.844756247467338</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.507714911916743</v>
+        <v>1.520694054315207</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.650724701955312</v>
+        <v>1.663835506330251</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.721022971300727</v>
+        <v>1.734065867595092</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.431292093324302</v>
+        <v>2.444358347624778</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.90565791760821</v>
+        <v>2.885864377319017</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.412839849607721</v>
+        <v>3.426038588562484</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.039987391852527</v>
+        <v>4.053392519505358</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.005688612989488</v>
+        <v>4.019145906699706</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.494617224880379</v>
+        <v>4.508069513600489</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.074362613935477</v>
+        <v>4.08791866028708</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.267265764393578</v>
+        <v>4.256836128695426</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>1630</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.135623604989284</v>
+        <v>2.148145894664907</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.792596895765072</v>
+        <v>2.805506705341124</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.968543639812253</v>
+        <v>1.981550771229855</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.485675987625157</v>
+        <v>1.498655130023621</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.560375557347584</v>
+        <v>1.573486361722523</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.980441652022172</v>
+        <v>1.993484548316538</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.815389111941791</v>
+        <v>2.828455366242267</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.242384074886509</v>
+        <v>3.219755821167979</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.10162958747722</v>
+        <v>4.114828326431983</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.846596426989173</v>
+        <v>4.860001554642004</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.641843102671594</v>
+        <v>4.655300396381811</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.289723192532357</v>
+        <v>5.303175481252467</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.930818274838991</v>
+        <v>4.944374321190594</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.241889300366807</v>
+        <v>5.231459664668655</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>1497</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.511902133728611</v>
+        <v>1.524424423404234</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.303532793127502</v>
+        <v>2.316442602703553</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.508130041137058</v>
+        <v>1.52113717255466</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.371360476815319</v>
+        <v>1.384339619213783</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.567251678298554</v>
+        <v>1.580362482673493</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.797937941781903</v>
+        <v>1.810980838076269</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.714539337994275</v>
+        <v>2.727605592294751</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.354510167562665</v>
+        <v>3.328627736224966</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.028313220592118</v>
+        <v>4.041511959546881</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.514193379585564</v>
+        <v>4.527598507238395</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.443040589670133</v>
+        <v>4.456497883380351</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.011825884624109</v>
+        <v>5.025278173344219</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.858772342483476</v>
+        <v>4.872328388835079</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.242094209161905</v>
+        <v>5.231664573463753</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>1373</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.218352072803128</v>
+        <v>1.230874362478751</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.717404369591414</v>
+        <v>1.730314179167465</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.249755459210256</v>
+        <v>1.262762590627858</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.598349203171466</v>
+        <v>1.61132834556993</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.86051022972957</v>
+        <v>1.873621034104509</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.157952167445231</v>
+        <v>2.170995063739596</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.456042322079803</v>
+        <v>3.469108576380279</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.415043470147438</v>
+        <v>4.384863804500377</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.0823757034116</v>
+        <v>5.095574442366363</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.251915485608727</v>
+        <v>5.265320613261558</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.119995373235795</v>
+        <v>5.133452666946013</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.809877438083049</v>
+        <v>5.823329726803159</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>5.680955674916731</v>
+        <v>5.694511721268334</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.857843795248371</v>
+        <v>5.847414159550219</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>1235</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.352715525943871</v>
+        <v>1.365237815619494</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.765433410955325</v>
+        <v>1.778343220531376</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.775423003953875</v>
+        <v>1.788430135371478</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.391506096075545</v>
+        <v>2.40448523847401</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.934056540922398</v>
+        <v>1.947167345297338</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.312470138557089</v>
+        <v>2.325513034851454</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.766197959746357</v>
+        <v>3.779264214046833</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.918447759345412</v>
+        <v>4.93162876864065</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.667164472353406</v>
+        <v>5.680363211308169</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.950642526191864</v>
+        <v>5.964047653844695</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>6.069775841550403</v>
+        <v>6.08323313526062</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.589988958410004</v>
+        <v>6.603441247130114</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>6.08876268754608</v>
+        <v>6.102318733897683</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.500427339660419</v>
+        <v>6.489997703962267</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>1090</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.543258927496446</v>
+        <v>1.555781217172068</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.399575222789068</v>
+        <v>1.412485032365119</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.922137708853029</v>
+        <v>1.935144840270631</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.511106437790808</v>
+        <v>2.524085580189272</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.339657699782862</v>
+        <v>2.352768504157801</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.637099637498522</v>
+        <v>2.650142533792888</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.836769589951004</v>
+        <v>3.84983584425148</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.020962337958501</v>
+        <v>5.034143347253739</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.602164286638576</v>
+        <v>5.615363025593339</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.128185890601479</v>
+        <v>6.14159101825431</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>6.015175685549956</v>
+        <v>6.028632979260173</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.69176067775777</v>
+        <v>6.70521296647788</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>6.363249186078924</v>
+        <v>6.376805232430527</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>6.521227399089156</v>
+        <v>6.510797763391004</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>913</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.7376679229444605</v>
+        <v>0.7501902126200832</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.988087738238697</v>
+        <v>1.000997547814748</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.907567333942211</v>
+        <v>1.920574465359813</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.037820466549711</v>
+        <v>2.050799608948175</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.061283150710835</v>
+        <v>1.074393955085775</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.125428264768225</v>
+        <v>2.13847116106259</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.57410090017941</v>
+        <v>3.587167154479886</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.859381904464726</v>
+        <v>4.872562913759964</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.565085194624153</v>
+        <v>5.578283933578916</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5.919779286704667</v>
+        <v>5.933184414357498</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.495967912003728</v>
+        <v>5.509425205713946</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.406583270882571</v>
+        <v>6.420035559602681</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>6.533973785896038</v>
+        <v>6.547529832247641</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>6.674166092980663</v>
+        <v>6.663736457282511</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>719</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.914072110944403</v>
+        <v>0.9265944006200257</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.8324011405392611</v>
+        <v>0.8453109501153122</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.550188901258387</v>
+        <v>1.563196032675989</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.124113800208022</v>
+        <v>1.137092942606486</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.8051279990087892</v>
+        <v>-0.7920171946338499</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.02221658126598</v>
+        <v>1.035259477560345</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.467385506552809</v>
+        <v>2.480451760853285</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.225515042402741</v>
+        <v>4.238696051697978</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.581761331463838</v>
+        <v>4.594960070418601</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.261538788995026</v>
+        <v>5.274943916647857</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.361375172605115</v>
+        <v>4.374832466315333</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.230250680437337</v>
+        <v>5.243702969157447</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.644488419979218</v>
+        <v>5.658044466330821</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>6.728702102742304</v>
+        <v>6.718272467044152</v>
       </c>
     </row>
     <row r="33">
@@ -3621,98 +3621,98 @@
         <v>509</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1588210118136004</v>
+        <v>0.1713433014892232</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.280056829104744</v>
+        <v>2.292966638680795</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.081651776732123</v>
+        <v>2.094658908149725</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2.211904909339623</v>
+        <v>2.224884051738087</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.2982381146996786</v>
+        <v>0.3113489190746179</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.970925631983114</v>
+        <v>1.983968528277479</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>3.261437494278617</v>
+        <v>3.274503748579093</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>6.134136217304579</v>
+        <v>6.147317226599817</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.483745368450379</v>
+        <v>5.496944107405142</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.812402108766257</v>
+        <v>5.825807236419088</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>4.232403204880903</v>
+        <v>4.245860498591121</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>5.838495596018078</v>
+        <v>5.851947884738188</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.025313676625238</v>
+        <v>5.038869722976841</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.25735328002137</v>
+        <v>6.246923644323218</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 95.57</t>
+          <t>X &gt; 95.56</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>286</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.094836921608582</v>
+        <v>-1.08231463193296</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.09079226262996798</v>
+        <v>0.1037020722060191</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.094524954634771</v>
+        <v>1.107532086052373</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2.273729136193325</v>
+        <v>2.286708278591789</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.735307921121155</v>
+        <v>1.748418725496094</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.732050558137516</v>
+        <v>2.745093454431881</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.696267889816284</v>
+        <v>3.70933414411676</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.026287288237576</v>
+        <v>6.039468297532814</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.468783905551774</v>
+        <v>2.481982644506537</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3.017260119125254</v>
+        <v>3.030665246778085</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.462856445157321</v>
+        <v>2.476313738867539</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.245491350754499</v>
+        <v>4.258943639474609</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>3.825236739809597</v>
+        <v>3.8387927861612</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>5.823209820337638</v>
+        <v>5.812780184639486</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>12.98275215598051</v>
+        <v>12.99527444565613</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>7.799749971587673</v>
+        <v>7.812659781163724</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>9.78583364594347</v>
+        <v>9.798840777361072</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>6.344658207122386</v>
+        <v>6.35763734952085</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>6.996713182526413</v>
+        <v>7.009823986901353</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>10.86558369167065</v>
+        <v>10.87862658796502</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>9.590373783922182</v>
+        <v>9.603440038222658</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>13.88509514704544</v>
+        <v>13.89827615634068</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.871714308482183</v>
+        <v>7.884913047436946</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>9.402541504406642</v>
+        <v>9.415946632059473</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>2.054931037231917</v>
+        <v>2.068388330942135</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>5.660742766005917</v>
+        <v>5.674195054726027</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>5.240488155061016</v>
+        <v>5.254044201412619</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>11.44259043971826</v>
+        <v>11.43216080402011</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Stoch-14 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Stoch-14 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,53 +3904,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 3.228</t>
+          <t>X &lt; 3.229</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.077990251218594</v>
+        <v>1.090512540894217</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.656892828730534</v>
+        <v>0.6698026383065852</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>2.655983634503919</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.798198935734753</v>
+        <v>-0.7852197933362888</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-3.717572531759302</v>
+        <v>-3.704461727384363</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-3.420130594043641</v>
+        <v>-3.407087697749276</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-5.8858166922683</v>
+        <v>-5.872750437967824</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-7.543476281525997</v>
+        <v>-7.530295272230759</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-8.794952358184482</v>
+        <v>-8.781753619229718</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.88317278130765</v>
+        <v>-4.869767653654819</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-7.468878486577609</v>
+        <v>-7.455421192867391</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-8.624971519708375</v>
+        <v>-8.611519230988264</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-8.795504798376989</v>
+        <v>-8.805934434075141</v>
       </c>
     </row>
     <row r="7">
@@ -3963,98 +3963,98 @@
         <v>168</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.625609298837638</v>
+        <v>7.638131588513261</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.799749971587673</v>
+        <v>7.812659781163724</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.000119360229178</v>
+        <v>8.01312649164678</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.154182016646203</v>
+        <v>5.167161159044667</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4.615760801574034</v>
+        <v>4.628871605948973</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.722726548813505</v>
+        <v>3.73576944510787</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.042754736303124</v>
+        <v>3.0558209906036</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.575571337521623</v>
+        <v>2.588752346816861</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1.919333356101227</v>
+        <v>1.93253209505599</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.259684361549496</v>
+        <v>2.273089489202327</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.459692941993815</v>
+        <v>1.473150235704033</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-2.077352472089323</v>
+        <v>-2.063900183369213</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.902368987796123</v>
+        <v>-1.88881294144452</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-4.033600036472215</v>
+        <v>-4.044029672170367</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 9.823</t>
+          <t>X &lt; 9.824</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>270</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7.506561679790025</v>
+        <v>7.519083969465647</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.15424732608502</v>
+        <v>5.167157135661071</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.129748989858811</v>
+        <v>5.142756121276413</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.000742863207051</v>
+        <v>6.013722005605516</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.832692018505249</v>
+        <v>5.845802822880188</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.389393215480169</v>
+        <v>5.402436111774534</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.675029868578264</v>
+        <v>5.68809612287874</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.467105729056023</v>
+        <v>4.480286738351261</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.517216953984828</v>
+        <v>5.530415692939592</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.185610287475413</v>
+        <v>3.199015415128244</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.980856963157834</v>
+        <v>2.994314256868051</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.904129009392165</v>
+        <v>1.917581298112275</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.854244768817622</v>
+        <v>1.867800815169225</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.9928549899828027</v>
+        <v>0.9824253542846506</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>395</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.747068008903952</v>
+        <v>6.759590298579575</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.882329838977668</v>
+        <v>4.895239648553719</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.500119360229178</v>
+        <v>5.51312649164678</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.630372492836678</v>
+        <v>5.643351635235142</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.091951277764508</v>
+        <v>5.105062082139447</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.136228658518142</v>
+        <v>5.149271554812508</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.798330384283837</v>
+        <v>4.811396638584313</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.318488757654237</v>
+        <v>3.331669766949474</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.270147099320035</v>
+        <v>4.283345838274798</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.166857357330088</v>
+        <v>3.180262484982919</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.215268589974528</v>
+        <v>3.228725883684746</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.983828962509833</v>
+        <v>1.997281251229943</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.816738908526958</v>
+        <v>1.830294954878561</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.306966569917165</v>
+        <v>1.296536934219013</v>
       </c>
     </row>
     <row r="10">
@@ -4116,49 +4116,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.333129945472677</v>
+        <v>4.3456522351483</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.644065557600669</v>
+        <v>3.65697536717672</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.647720836243934</v>
+        <v>5.660727967661536</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.301959208703842</v>
+        <v>4.314938351102306</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.579036148613213</v>
+        <v>3.592146952988152</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.846957791125924</v>
+        <v>1.860000687420289</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.762224073853645</v>
+        <v>1.775290328154121</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.5570332949983481</v>
+        <v>0.5702143042935859</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.603044478926741</v>
+        <v>1.616243217881504</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.7529192938988132</v>
+        <v>0.7663244215516443</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1791622795443359</v>
+        <v>0.1926195732545537</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.3980472819082195</v>
+        <v>0.4114995706283295</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1622945159817633</v>
+        <v>0.1758505623333662</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.5920015856316283</v>
+        <v>-0.5209230125323501</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.548857752297586</v>
+        <v>3.561380041973209</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.541513746584073</v>
+        <v>2.554423556160124</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.110391263552444</v>
+        <v>4.123398394970046</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3.032185181658427</v>
+        <v>3.045164324056891</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.94693617202433</v>
+        <v>2.960046976399269</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.129574484362344</v>
+        <v>1.142617380656709</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.893783365277379</v>
+        <v>0.906849619577855</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.02657223894218674</v>
+        <v>-0.01339122964694894</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.969829687564328</v>
+        <v>0.9830284265190912</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.7239341097871588</v>
+        <v>0.7373392374399899</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.3681233836568865</v>
+        <v>0.3815806773671042</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.1003917373769454</v>
+        <v>0.1138440260970555</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.5864815373081669</v>
+        <v>0.6000375836597698</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.317671485752399</v>
+        <v>0.3726010284482442</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.868157689765091</v>
+        <v>2.880679979440714</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.8825192388955898</v>
+        <v>0.895429048471641</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.732039559730431</v>
+        <v>2.745046691148033</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.488227854432687</v>
+        <v>2.501206996831151</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.448559756567505</v>
+        <v>2.461670560942444</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.8756775047569789</v>
+        <v>0.8887204010513443</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.4168789495794627</v>
+        <v>0.4299452038799387</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.4243692871072753</v>
+        <v>-0.4111882778120375</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.6100574525913274</v>
+        <v>-0.5968587136365642</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.5873646825070296</v>
+        <v>-0.5739595548541985</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.166182844729846</v>
+        <v>-1.152725551019628</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.6330465701774344</v>
+        <v>-0.6195942814573243</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.8039246225188492</v>
+        <v>-0.7903685761672463</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.7341529168003831</v>
+        <v>-0.6893212052424573</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.677742611534335</v>
+        <v>1.690264901209957</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.4995384460240402</v>
+        <v>0.5124482556000913</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.946489891106751</v>
+        <v>1.959497022524353</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.53503121439681</v>
+        <v>1.548010356795274</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.321637084915103</v>
+        <v>1.334747889290043</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.3310834909120288</v>
+        <v>-0.3180405946176634</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.8491866556382632</v>
+        <v>-0.8361204013377872</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.316370054419764</v>
+        <v>-1.303189045124526</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.9440004931481099</v>
+        <v>-0.9308017541933467</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.144071506995104</v>
+        <v>-1.130666379342273</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.240482469449191</v>
+        <v>-1.227025175738973</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.9894145883767962</v>
+        <v>-0.9759622996566861</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.409669199321698</v>
+        <v>-1.396113152970095</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.31693853456126</v>
+        <v>-1.278719864607048</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.7829149561432942</v>
+        <v>0.7448904210785443</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1638913253869561</v>
+        <v>-0.1509815158109049</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.8657413925178759</v>
+        <v>0.878748523935478</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.9010277634919461</v>
+        <v>0.9140069058904103</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.122340641487206</v>
+        <v>1.135451445862145</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1852146779682968</v>
+        <v>0.1982575742626622</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.7542198940048337</v>
+        <v>-0.7411536397043577</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.506303577686616</v>
+        <v>-1.493122568391378</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.9975028940683544</v>
+        <v>-0.9843041551135912</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.562727794195993</v>
+        <v>-1.549322666543162</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.577547595246713</v>
+        <v>-1.564090301536496</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.205996325067773</v>
+        <v>-1.244811864280891</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.002998773487761</v>
+        <v>-1.042352684337878</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.6050286079007918</v>
+        <v>-0.5734121197259938</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.6818368703065403</v>
+        <v>0.6493716175197903</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1676706969337545</v>
+        <v>-0.1547608873577033</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.1995266421936179</v>
+        <v>0.2125337736112201</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.007171815444636</v>
+        <v>1.0201509578431</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.230816646096436</v>
+        <v>1.243927450471375</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1652215177967165</v>
+        <v>-0.1521786215023511</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.6733252604711879</v>
+        <v>-0.6602590061707119</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.64855268973534</v>
+        <v>-1.635371680440102</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.624878570837197</v>
+        <v>-1.611679831882434</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.051633730462918</v>
+        <v>-2.038228602810086</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.917691034458741</v>
+        <v>-1.904233740748523</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.83723947773904</v>
+        <v>-1.8698555883932</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.447988762423535</v>
+        <v>-1.481226177925556</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.236284166151258</v>
+        <v>-1.208697065845399</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.09435225775757061</v>
+        <v>-0.1217075069422719</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.6396653985207621</v>
+        <v>-0.626755588944711</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.412533678584083</v>
+        <v>0.4255408100016851</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.9235941226919735</v>
+        <v>0.9365732650904377</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.3090114453197259</v>
+        <v>0.3221222496946652</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.6121300137658281</v>
+        <v>-0.5990871174714627</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.306155429438725</v>
+        <v>-1.293089175138249</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.001823215120446</v>
+        <v>-1.988642205825208</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.062823101302747</v>
+        <v>-2.049624362347984</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.227495125629993</v>
+        <v>-2.214089997977162</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.162548637564832</v>
+        <v>-2.190306769337127</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.010609527772004</v>
+        <v>-2.038493679304175</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.320762299319213</v>
+        <v>-1.349420983288262</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.02876173751627</v>
+        <v>-1.005134724878481</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6534148266431714</v>
+        <v>0.6287974565376189</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.3005824724201744</v>
+        <v>0.3134922819962256</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.063450360928968</v>
+        <v>1.037602016122307</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.333661506132685</v>
+        <v>1.34664064853115</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.005177309954853</v>
+        <v>1.018288114329792</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.02698187199359126</v>
+        <v>-0.01393897569922586</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.3916316144583121</v>
+        <v>-0.378565360157836</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.628584082519019</v>
+        <v>-1.615403073223781</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.75956297499944</v>
+        <v>-1.746364236044677</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.979877103344371</v>
+        <v>-1.96647197569154</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.796609579014586</v>
+        <v>-1.821278102461179</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.653970084796633</v>
+        <v>-1.678746121744567</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.264554254609727</v>
+        <v>-1.289820716663939</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.326833119178985</v>
+        <v>-1.305767466867493</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.4032871205960689</v>
+        <v>0.3825200928136638</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.1377575251137841</v>
+        <v>-0.124847715537733</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.5095711560703933</v>
+        <v>0.4879375747701999</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.017896122326277</v>
+        <v>1.030875264724742</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.5424868795288447</v>
+        <v>0.5555976839037839</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.2312747114259395</v>
+        <v>-0.2182318151315741</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.3790204009729479</v>
+        <v>-0.3659541466724718</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.9722277443039218</v>
+        <v>-0.959046735008684</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.096239602760953</v>
+        <v>-1.08304086380619</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.505280981865752</v>
+        <v>-1.491875854212921</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.549524616404064</v>
+        <v>-1.570553067923655</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.228246268093528</v>
+        <v>-1.249482360754669</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.171849507276647</v>
+        <v>-1.193304454137937</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.202928917740451</v>
+        <v>-1.185083063223757</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.07361324732367791</v>
+        <v>-0.09163864125696364</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.6939332159730682</v>
+        <v>-0.6810234063970171</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.1241513515561223</v>
+        <v>-0.1428501847380588</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.1811309525799629</v>
+        <v>0.1941100949784271</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.06557497661121658</v>
+        <v>-0.05246417223627731</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.5849358393623092</v>
+        <v>-0.5718929430679438</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.019727899691759</v>
+        <v>-1.006661645391283</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.48691129847326</v>
+        <v>-1.473730289178022</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.722940356184154</v>
+        <v>-1.70974161722939</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.249947862618626</v>
+        <v>-2.26794512767826</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.897561174606089</v>
+        <v>-1.915849847691845</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.00673100316277</v>
+        <v>-2.024959373400371</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.751993047946499</v>
+        <v>-1.770530678217789</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.996764237202257</v>
+        <v>-1.980537608678311</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.6556004823721366</v>
+        <v>-0.6710835075737904</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.049306146262388</v>
+        <v>-1.06507509657115</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.603776743666927</v>
+        <v>-0.6199183974824791</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.4194110569468776</v>
+        <v>-0.4064319145484134</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3084816226683884</v>
+        <v>-0.2953708182934491</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.685322539798662</v>
+        <v>-0.7014599921215705</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.203191070281548</v>
+        <v>-1.190124815981072</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.562090765760402</v>
+        <v>-1.548909756465164</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.568948800291381</v>
+        <v>-1.555750061336617</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.227495125629993</v>
+        <v>-2.243243302712493</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.077860290681372</v>
+        <v>-2.093764070646891</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.393693759146444</v>
+        <v>-2.409428638653765</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.970839132229372</v>
+        <v>-1.986943299878575</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.342891179639587</v>
+        <v>-2.328400392786349</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.9891037970075303</v>
+        <v>-1.002832442359022</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.247869076031371</v>
+        <v>-1.261913444352899</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.8500593023537775</v>
+        <v>-0.8644245287613757</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7198061697462776</v>
+        <v>-0.7068270273478134</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.6179567916941195</v>
+        <v>-0.6325591531846939</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.8548581897318854</v>
+        <v>-0.8692697104930858</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.70607121206293</v>
+        <v>-1.693004957762454</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.713367027809177</v>
+        <v>-1.700186018513939</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.029860015677734</v>
+        <v>-2.016661276722971</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.699415842949477</v>
+        <v>-2.713284212041081</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.621113293543878</v>
+        <v>-2.635088151675447</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.917509415112178</v>
+        <v>-2.931334113462988</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.747223058456647</v>
+        <v>-2.761260180319603</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.03340487644099</v>
+        <v>-3.019964131975797</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.8774228836446127</v>
+        <v>-0.8897877759538346</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.209259037421333</v>
+        <v>-1.221865751191039</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.9025846474965604</v>
+        <v>-0.9154449369246507</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.9396758163420671</v>
+        <v>-0.9524957814717609</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.6306200127139903</v>
+        <v>-0.6437301883919559</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.5970671326823052</v>
+        <v>-0.6101303454511751</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.358783441830788</v>
+        <v>-1.345717187530312</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.874322740032028</v>
+        <v>-1.86114173073679</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.080390324473512</v>
+        <v>-2.067191585518749</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.469391593941559</v>
+        <v>-2.481907287071053</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.599796294165309</v>
+        <v>-2.612308330886606</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.878401705341943</v>
+        <v>-2.890779821962305</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.691405532646627</v>
+        <v>-2.703986468482455</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.803306658820624</v>
+        <v>-2.791261122890198</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.212560003650047</v>
+        <v>-1.2234857607584</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.610732756972858</v>
+        <v>-1.62183679880404</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.065814705704888</v>
+        <v>-1.077262524371527</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.048509779265927</v>
+        <v>-1.059945068061559</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.8292219577991986</v>
+        <v>-0.8408838638064964</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.7820877565510074</v>
+        <v>-0.7937142090320606</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.233625692071804</v>
+        <v>-1.220559437771328</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.609108036291168</v>
+        <v>-1.59592702699593</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.829028373911875</v>
+        <v>-1.840311292642966</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.333401151682878</v>
+        <v>-2.344647513855783</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.146170891142745</v>
+        <v>-2.157556291973577</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.454400397368751</v>
+        <v>-2.465644903295747</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.252509043818542</v>
+        <v>-2.263946917864672</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.529494946160241</v>
+        <v>-2.518732053122754</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.319525276731717</v>
+        <v>-1.329242844962863</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.429935813122036</v>
+        <v>-1.439928210554704</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.149140866054552</v>
+        <v>-1.159339798044392</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.9956614644989799</v>
+        <v>-1.005908591048588</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.8575260741518704</v>
+        <v>-0.8679461895192375</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.7108246494435733</v>
+        <v>-0.7212572680164087</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.231288214210409</v>
+        <v>-1.218221959909933</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.567752658743544</v>
+        <v>-1.554571649448306</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.954125356067159</v>
+        <v>-1.964137683966733</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.38852031936343</v>
+        <v>-2.398517601759607</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.438960760324811</v>
+        <v>-2.44898338006238</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.68662062282408</v>
+        <v>-2.696535436423311</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.472134011709628</v>
+        <v>-2.482232325784906</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.635609647656146</v>
+        <v>-2.625855415568168</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.603905841931123</v>
+        <v>-1.61242967817703</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.456005310657673</v>
+        <v>-1.464878292402481</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.207955173932312</v>
+        <v>-1.217005958684346</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.9313507880249645</v>
+        <v>-0.9404992964418781</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.033204130441042</v>
+        <v>-1.042410991597087</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.045100980208055</v>
+        <v>-1.054256801611288</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.522383222654817</v>
+        <v>-1.53136214135565</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.90661348995561</v>
+        <v>-1.893432480660373</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.235971919535992</v>
+        <v>-2.244750597365645</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.690502437952382</v>
+        <v>-2.6992479935086</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.665445485470187</v>
+        <v>-2.674243466484185</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.024243484414484</v>
+        <v>-3.032892431431229</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.715811571812274</v>
+        <v>-2.724668679668355</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.901038903911093</v>
+        <v>-2.892147472906629</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.335212957037612</v>
+        <v>-1.342768463815361</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.591264878971558</v>
+        <v>-1.598972952023779</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.140352152540963</v>
+        <v>-1.148303201990302</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.7925834820060942</v>
+        <v>-0.800656223311023</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.8380526545988403</v>
+        <v>-0.8461957794957726</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.070087508359329</v>
+        <v>-1.078098689641116</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.566651009466256</v>
+        <v>-1.574485105084079</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.876416069011235</v>
+        <v>-1.863235059715997</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.388878117464579</v>
+        <v>-2.396472233948337</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.8637238043951</v>
+        <v>-2.871267466178253</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.73230300532127</v>
+        <v>-2.739935155994978</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-3.149813383927452</v>
+        <v>-3.15728079802642</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.918216967366504</v>
+        <v>-2.925845807409203</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-3.160114547602113</v>
+        <v>-3.152111390662185</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2668</v>
+        <v>2669</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.8143338425980389</v>
+        <v>-0.8210876083038414</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.100159376250012</v>
+        <v>-1.107027496732513</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.7284093925714217</v>
+        <v>-0.7354737323173879</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.6154250417169251</v>
+        <v>-0.6225184170426843</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.7226974516824285</v>
+        <v>-0.7298277198777399</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.8162142611553449</v>
+        <v>-0.8232739031731526</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.292199140535566</v>
+        <v>-1.299096677398182</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.684588223685054</v>
+        <v>-1.671407214389816</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.024870588102708</v>
+        <v>-2.031566633440647</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.293708852023357</v>
+        <v>-2.300423417643913</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.253692449601978</v>
+        <v>-2.26045398442713</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.573607153737257</v>
+        <v>-2.580248617164294</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.486679144980023</v>
+        <v>-2.493414332562772</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.74138899913374</v>
+        <v>-2.734461258817767</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2792</v>
+        <v>2793</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.5676180634339403</v>
+        <v>-0.5736076526377403</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.662272011661571</v>
+        <v>-0.6684216671074523</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.5027357432683175</v>
+        <v>-0.5089926663981714</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.6388170823150574</v>
+        <v>-0.6450138180125364</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.7651915793783459</v>
+        <v>-0.7714106061861514</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.8771305430050091</v>
+        <v>-0.8832781739397504</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.478757228025131</v>
+        <v>-1.484703686577028</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.9816804409596</v>
+        <v>-1.968499431664362</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.27393494156464</v>
+        <v>-2.279660287257904</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.354049544029898</v>
+        <v>-2.359850565618316</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.289135748695344</v>
+        <v>-2.29498792084614</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.629130090796075</v>
+        <v>-2.634860231073439</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.564739199038527</v>
+        <v>-2.570545906642053</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.689624050662424</v>
+        <v>-2.683485454483296</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.5396496691736132</v>
+        <v>-0.5447747261865246</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.5700017360294396</v>
+        <v>-0.5752825517327338</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.640649085877584</v>
+        <v>-0.6459489672247329</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.8662261466190984</v>
+        <v>-0.87143925221811</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.6719139825281033</v>
+        <v>-0.6772508430306203</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.7984896980664615</v>
+        <v>-0.8037564707365306</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.375626507920813</v>
+        <v>-1.380708556545414</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.892769132181236</v>
+        <v>-1.897725594717258</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.174120038885384</v>
+        <v>-2.178989897937392</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.290417887939256</v>
+        <v>-2.295337540894216</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.34045480206801</v>
+        <v>-2.345381266876551</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.560526642166629</v>
+        <v>-2.565377623987466</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.348340621075849</v>
+        <v>-2.353309790661697</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.557897127322221</v>
+        <v>-2.552583554316882</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.5180497191737103</v>
+        <v>-0.5223533889027507</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3311214245898455</v>
+        <v>-0.3356254396603546</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5789473928492441</v>
+        <v>-0.5834073599891099</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.7553649463853631</v>
+        <v>-0.7597591878367922</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.6927439232731061</v>
+        <v>-0.6972069616206795</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.7669480105983197</v>
+        <v>-0.7713641476288373</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.158675998223003</v>
+        <v>-1.16297486377448</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.608483004760565</v>
+        <v>-1.612678387709266</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.78196534519747</v>
+        <v>-1.786112129917342</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.965172193609106</v>
+        <v>-1.969334753221922</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.924926012800569</v>
+        <v>-1.929121683131697</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.165371104956826</v>
+        <v>-2.169488227553749</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.047888834226242</v>
+        <v>-2.052082669225143</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.138129653196962</v>
+        <v>-2.133694666906884</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3252</v>
+        <v>3253</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1810340323079842</v>
+        <v>-0.1845290127756272</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.122168795919336</v>
+        <v>-0.1257927820974203</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4392002842697522</v>
+        <v>-0.4427558612944011</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.4456544844778563</v>
+        <v>-0.4492012302260946</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1702382346549953</v>
+        <v>-0.1739078749421026</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.4388276434155358</v>
+        <v>-0.4423967615772</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.8137817414361663</v>
+        <v>-0.8172435726450118</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.20303955434894</v>
+        <v>-1.206415612972144</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.370284609599018</v>
+        <v>-1.373615409986542</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.466769364904231</v>
+        <v>-1.470130242657262</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.347526720064558</v>
+        <v>-1.350940088386288</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.603576606488012</v>
+        <v>-1.606910936057382</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.638144023294494</v>
+        <v>-1.641498281099743</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.709755369454122</v>
+        <v>-1.706260872673937</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3446</v>
+        <v>3447</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1661761056971187</v>
+        <v>-0.1687773022106569</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.02751048725173888</v>
+        <v>-0.03023453180864522</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2331754040172811</v>
+        <v>-0.2358613626042327</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1161552849411009</v>
+        <v>-0.1188699441689636</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.2873203081552447</v>
+        <v>0.2844602302875998</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.06515223906529144</v>
+        <v>-0.06789673916613026</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.3368116862693782</v>
+        <v>-0.3394832804968431</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.7303106908401205</v>
+        <v>-0.7328934270443739</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.7755376957677882</v>
+        <v>-0.7781118380676588</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.9142286819287619</v>
+        <v>-0.9168071591121745</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.7260682862434891</v>
+        <v>-0.7287131183332249</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.9075922246028512</v>
+        <v>-0.9101841304069964</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.9926752582590552</v>
+        <v>-0.9952652671543873</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.249143247372366</v>
+        <v>-1.246566039197596</v>
       </c>
     </row>
     <row r="33">
@@ -5312,101 +5312,101 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3656</v>
+        <v>3657</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.0004292186289447386</v>
+        <v>-0.001351997836806618</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.179166785955033</v>
+        <v>-0.1809546719764796</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2048165546876461</v>
+        <v>-0.2066117853434051</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1961414187836183</v>
+        <v>-0.1979355204779765</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.07148743056123408</v>
+        <v>0.06960108923163943</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1346242517687415</v>
+        <v>-0.1364451979116836</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.2863860928376951</v>
+        <v>-0.2881694439981857</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.7114042938013512</v>
+        <v>-0.7130884550239358</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.5936412410033824</v>
+        <v>-0.5953605475280739</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.6364905018384803</v>
+        <v>-0.6382280014650661</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.4161448487114257</v>
+        <v>-0.4179504668720782</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.6398638626488307</v>
+        <v>-0.6416081181419244</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.5253620734635334</v>
+        <v>-0.5271529138468338</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.7252745180810507</v>
+        <v>-0.7235874673967473</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 95.57</t>
+          <t>X &lt; 95.56</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3879</v>
+        <v>3880</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1016284834899182</v>
+        <v>0.1006406095889432</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1226930269902482</v>
+        <v>0.1216697160729368</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.001165986814527287</v>
+        <v>-0.002165207145303327</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.06260770772902191</v>
+        <v>-0.06358923880085143</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.02121744651532964</v>
+        <v>-0.02221999551547782</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.06982983571612777</v>
+        <v>-0.07081491703204534</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1147949536706463</v>
+        <v>-0.1157705171083023</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.3105290485787506</v>
+        <v>-0.3114633235995257</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.02269989386199001</v>
+        <v>-0.02370986118596363</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.06025726434114631</v>
+        <v>-0.06127371024841466</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.01874232701332801</v>
+        <v>-0.01977374305563018</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1502288785137864</v>
+        <v>-0.1512263039256183</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1178819971235683</v>
+        <v>-0.1188960079099672</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2918403782392502</v>
+        <v>-0.2909614345660501</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4081</v>
+        <v>4082</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.2462473089740129</v>
+        <v>-0.2464837961021118</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.03709109271491684</v>
+        <v>-0.03738790767243216</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1254915879624221</v>
+        <v>-0.1257691838968285</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.03083503588490544</v>
+        <v>-0.03113516828392449</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.04252304986385269</v>
+        <v>-0.04282352040272031</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.09850113521682147</v>
+        <v>-0.09878638211299062</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.04759099102889763</v>
+        <v>-0.04788931229965243</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1588537268520582</v>
+        <v>-0.1591276270905055</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.01060161348132027</v>
+        <v>-0.01091227559660268</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.03937724595765246</v>
+        <v>-0.03968584119414942</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1123910437614555</v>
+        <v>0.1120439816969281</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.03812634250779467</v>
+        <v>0.03779749864189341</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.04812213466951221</v>
+        <v>0.04778829714054922</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1048244095833795</v>
+        <v>-0.1045508919272606</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/stoch/stoch_14.xlsx
+++ b/workspaces/btc_daily_14days/stoch/stoch_14.xlsx
@@ -568,209 +568,209 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 4.877</t>
+          <t>X ≈ 4.885</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>14.1397659828179</v>
+        <v>15.06233339008536</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>14.91108894727471</v>
+        <v>14.64091966571221</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.33364078438519</v>
+        <v>13.07443000504288</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11.09208689756887</v>
+        <v>10.86023098078171</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>12.93348886737397</v>
+        <v>12.71655322676997</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.85729056312799</v>
+        <v>10.11247756214168</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11.96391789005685</v>
+        <v>11.22894730980654</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>12.68917866544322</v>
+        <v>11.94127010977939</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>12.63143537049871</v>
+        <v>11.90731160619887</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>9.406789264026443</v>
+        <v>9.911814856434646</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>10.3941531769608</v>
+        <v>10.88586652043122</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4.481642818357145</v>
+        <v>5.067235374612288</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.872446562753758</v>
+        <v>3.497171252014596</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7178750897349317</v>
+        <v>0.2176049417374912</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 8.175</t>
+          <t>X ≈ 8.182</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.29765596811415</v>
+        <v>6.873730624132193</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.8067521515948499</v>
+        <v>1.347899607715483</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4131897301946239</v>
+        <v>0.9554168547764021</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.388796921284111</v>
+        <v>8.000405801030041</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7.831858188751617</v>
+        <v>8.502350029105706</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.130778105373899</v>
+        <v>8.7747284916029</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>10.00567450069292</v>
+        <v>10.69317759601515</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>7.584106863155931</v>
+        <v>8.253615239714655</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>11.44175160435661</v>
+        <v>12.17419157649559</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.719287958594997</v>
+        <v>4.430654145680158</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>5.495603047611716</v>
+        <v>5.217157289489727</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8.471092371887842</v>
+        <v>8.245460901354157</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.053158834850009</v>
+        <v>7.852454043523402</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.261292456680728</v>
+        <v>10.08365036981069</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 11.47</t>
+          <t>X ≈ 11.48</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>125</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.099785305408112</v>
+        <v>5.072185682774332</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.293508880324893</v>
+        <v>4.293527351125483</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.293960523284603</v>
+        <v>6.295567095797566</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.829717831701366</v>
+        <v>4.830594564076158</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3.496006536745959</v>
+        <v>3.545447250853094</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.592178388983726</v>
+        <v>4.616112785981514</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.911880620009136</v>
+        <v>2.9598153859571</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.8490237637315161</v>
+        <v>0.8981932124651024</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.587272808463318</v>
+        <v>1.660434010037839</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.136365427392619</v>
+        <v>3.235610225317821</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>3.732049865234274</v>
+        <v>3.831881817223021</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.168298572873276</v>
+        <v>2.291928336886329</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.748827532388319</v>
+        <v>1.897476226338625</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.975017946877244</v>
+        <v>2.147016706443907</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 14.77</t>
+          <t>X ≈ 14.78</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>147</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.13557245521875</v>
+        <v>-1.838739708927768</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.3273306594734748</v>
+        <v>-0.03782121229979651</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.037518089876947</v>
+        <v>6.353257494056713</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.742014893838018</v>
+        <v>1.055338449362104</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4730474991554772</v>
+        <v>-0.1150880916195192</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-6.964033485788065</v>
+        <v>-6.630792788892094</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.371307257204265</v>
+        <v>-6.014624312518308</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-6.839050499618672</v>
+        <v>-6.78992497096484</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-5.543205682669139</v>
+        <v>-5.470080832805856</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-5.713984411891779</v>
+        <v>-5.614776036778146</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-7.959177789060796</v>
+        <v>-7.859380106905647</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.84751421708723</v>
+        <v>-3.723899236749574</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-4.268593782731024</v>
+        <v>-4.119953065013767</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.404573889857758</v>
+        <v>-5.912847239134322</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.01670325515489424</v>
+        <v>-0.04788607818726121</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.418545689456302</v>
+        <v>-2.465610153759634</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.81375711388732</v>
+        <v>-3.684590776281354</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.683839638979038</v>
+        <v>-2.731335556406215</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1037116656261148</v>
+        <v>-0.7499612488141381</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.09309839295662</v>
+        <v>-2.127430593221838</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.009788176449931</v>
+        <v>-3.014584813597622</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.644716204833728</v>
+        <v>-2.659461206212043</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.874418583291906</v>
+        <v>-1.871022907544173</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.6057984293807124</v>
+        <v>0.6005750246804737</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.234122796077848</v>
+        <v>0.8591336247966481</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.229800690440207</v>
+        <v>-1.560474437577241</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.515273737449299</v>
+        <v>2.175074715713535</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.408351280210773</v>
+        <v>4.0775952188406</v>
       </c>
     </row>
     <row r="11">
@@ -832,205 +832,205 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3392480498933281</v>
+        <v>-0.7379187864874197</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-6.92574471153943</v>
+        <v>-6.652281486230493</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-3.762537141911608</v>
+        <v>-3.457699547524186</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.0720811547332687</v>
+        <v>0.2622355046729226</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1036075718536367</v>
+        <v>0.4848334167949488</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.311276362733814</v>
+        <v>0.7564949861096508</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.821335210000626</v>
+        <v>-0.7432250439625037</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.287852255306987</v>
+        <v>-1.217489956926265</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-8.055508785327071</v>
+        <v>-7.325657533084708</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-6.766436176243658</v>
+        <v>-6.314973822851897</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-8.400214537147626</v>
+        <v>-7.956432834093739</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.085186718346279</v>
+        <v>-3.586670152148166</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-7.362794425477155</v>
+        <v>-6.859691415860603</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-5.710696338836875</v>
+        <v>-5.173846602908448</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 24.66</t>
+          <t>X ≈ 24.67</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>121</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-6.177804526329957</v>
+        <v>-7.074280782208525</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.018752060505179</v>
+        <v>-2.915717505788407</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.238123318104549</v>
+        <v>-3.308764638239118</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.756665679772091</v>
+        <v>-4.829956949573571</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-6.118910128351892</v>
+        <v>-6.154726320927992</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-8.29625501995973</v>
+        <v>-8.36116877142058</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-9.207683694170591</v>
+        <v>-9.625426838102989</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-7.201669657147676</v>
+        <v>-6.79248412511523</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.138868132902957</v>
+        <v>-2.700668840436016</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.8142375688955</v>
+        <v>-4.356773055355177</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.71747418874665</v>
+        <v>-1.259874815859973</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.335741017823992</v>
+        <v>-3.212147033183399</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-5.409263891486773</v>
+        <v>-5.260637459847374</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-5.185312631635156</v>
+        <v>-5.013313872068494</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 27.96</t>
+          <t>X ≈ 27.97</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-6.026160962966642</v>
+        <v>-5.612482411794616</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.921606731892766</v>
+        <v>-4.921254171243753</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-6.874995420948451</v>
+        <v>-6.852490207925349</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.630045466176689</v>
+        <v>-3.648498734425132</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2799258642225624</v>
+        <v>-0.6507022608047919</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.913426303489352</v>
+        <v>3.465648255179154</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.07378065774834397</v>
+        <v>-0.4417416839804318</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.889931414040035</v>
+        <v>-3.218602529791788</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.390813677306561</v>
+        <v>-1.71737956153288</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.59720056297116</v>
+        <v>-4.854726040666328</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-4.026108984604818</v>
+        <v>-3.522708030443731</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.210295278387264</v>
+        <v>-2.694651291188499</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.495812429202957</v>
+        <v>1.190074219472862</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.512517946877246</v>
+        <v>3.747016706443908</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 31.26</t>
+          <t>X ≈ 31.27</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>128</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.1374588233270302</v>
+        <v>-0.1664177711786721</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1845249631045007</v>
+        <v>-0.1866117909349327</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.25289133098579</v>
+        <v>-5.26489605894556</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.887818878912185</v>
+        <v>1.892154440154712</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.130731741712545</v>
+        <v>2.184044104674541</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-3.028786223680115</v>
+        <v>-3.010084957754437</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.005962224982305031</v>
+        <v>0.05335504911619893</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.800945050674073</v>
+        <v>-2.755221455010513</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-6.765497262324075</v>
+        <v>-6.697172709459828</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-6.055703616263031</v>
+        <v>-5.958680969954123</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.700626512126874</v>
+        <v>-4.600778708114071</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-7.011816850036055</v>
+        <v>-6.885633325437801</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-5.088217703349287</v>
+        <v>-4.937705833249083</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.252983293556269</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-7.056744406770491</v>
+        <v>-7.046019013932224</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.872370155241619</v>
+        <v>-4.845518633881653</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.34245060332745</v>
+        <v>2.329539302366662</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1911600747471027</v>
+        <v>0.1881401698152061</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-7.967051065691962</v>
+        <v>-7.874070901282764</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.625916431328235</v>
+        <v>-4.571946879012401</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-7.001184569320657</v>
+        <v>-6.904432151061656</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-5.188589376438259</v>
+        <v>-5.098051400139376</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.015091123914367</v>
+        <v>-5.892312049868025</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.822488312612194</v>
+        <v>-3.686545908244035</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.79341000744963</v>
+        <v>-4.647951103736887</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.558811124844695</v>
+        <v>-3.832496325779807</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.162168085028668</v>
+        <v>-0.4410044156647714</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.826926343823807</v>
+        <v>0.5651985246258988</v>
       </c>
     </row>
     <row r="16">
@@ -1092,101 +1092,101 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>9.108551587333466</v>
+        <v>9.015374942542842</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>10.92429346013196</v>
+        <v>10.8526626774155</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>7.95465479554872</v>
+        <v>7.900317531076958</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.972187344659062</v>
+        <v>5.4698072025516</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>8.878715961636253</v>
+        <v>8.398409511299086</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>6.598119157174864</v>
+        <v>6.10807635197623</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>9.959537143088269</v>
+        <v>9.465131994781331</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.607620657734799</v>
+        <v>2.164447342617414</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.685841218896194</v>
+        <v>1.273123010110439</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.8364542912323785</v>
+        <v>0.4496246710580039</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.355744652781205</v>
+        <v>1.954327387930732</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.390122805136343</v>
+        <v>2.012456020477316</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.6162349447286033</v>
+        <v>-0.9458332858346736</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-4.70084412208827</v>
+        <v>-4.970932011505006</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 41.15</t>
+          <t>X ≈ 41.16</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>158</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.843215465245265</v>
+        <v>-1.874728177462082</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-4.079400713516854</v>
+        <v>-4.08849093024503</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-4.475899072672064</v>
+        <v>-4.483896045118541</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.821562265641127</v>
+        <v>-1.825013532685681</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.621580736553497</v>
+        <v>-3.579329769366346</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.061552484311491</v>
+        <v>-2.041111848776715</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.2508555817552818</v>
+        <v>-0.2036544609269058</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.972658478165414</v>
+        <v>5.024923461077982</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.913330876781302</v>
+        <v>4.988007052870813</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.799917155192745</v>
+        <v>2.899209727953895</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.6970803140645003</v>
+        <v>0.7971103558988375</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.630192643635013</v>
+        <v>2.753236017782697</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.3216037792987976</v>
+        <v>-0.1725057076753203</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.09586812907212305</v>
+        <v>0.07613063049453928</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-6.053748103453536</v>
+        <v>-6.043886856564036</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-7.675508792092828</v>
+        <v>-7.626930939575992</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-8.073199503473752</v>
+        <v>-8.023964938816135</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-10.31579589291017</v>
+        <v>-10.25868937556736</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-7.694831761938353</v>
+        <v>-7.599281789165687</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-5.024781625162632</v>
+        <v>-4.965172242052418</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-9.076521864985693</v>
+        <v>-8.961159364827573</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-7.967118286828473</v>
+        <v>-7.852514839338582</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-9.619647631235146</v>
+        <v>-9.46358850985451</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-12.06992865753231</v>
+        <v>-11.86114192755526</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.555615139854382</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-11.78612240559143</v>
+        <v>-12.00711563772646</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-9.031670084301489</v>
+        <v>-9.253789273162603</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-11.98053760867831</v>
+        <v>-12.15849510457971</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-8.141051039125699</v>
+        <v>-7.766553112907296</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-6.029102415303861</v>
+        <v>-5.654841240777529</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-6.762898171416175</v>
+        <v>-6.796098423847376</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-8.131462692115853</v>
+        <v>-8.494192081180955</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.423274119791294</v>
+        <v>-3.764711484705643</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.377194791291096</v>
+        <v>-2.746263292650937</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.548644873167774</v>
+        <v>-4.302486612713821</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.514533210313239</v>
+        <v>-3.281235910992493</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.4292095979840767</v>
+        <v>-0.3349518437062429</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.924905498266348</v>
+        <v>-2.660407490167458</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-4.385245754270898</v>
+        <v>-5.103050916112316</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-7.35838639890806</v>
+        <v>-8.030261797353582</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-4.771018455228983</v>
+        <v>-5.442163047494354</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-6.800921902746815</v>
+        <v>-6.999251950272509</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-6.586617204769802</v>
+        <v>-6.557726777715786</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.583303071880827</v>
+        <v>-4.54120358735279</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.977762159945797</v>
+        <v>-4.937477348807789</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-5.753113927158822</v>
+        <v>-5.708494208494209</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-6.29772580520487</v>
+        <v>-6.197743349445929</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.682428382882321</v>
+        <v>-4.123156028825193</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-10.12146164436733</v>
+        <v>-10.49011842435696</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.235111522026301</v>
+        <v>-4.649644878434209</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-9.750694670451303</v>
+        <v>-10.09202289297662</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-10.60569838958556</v>
+        <v>-10.91585147379139</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-11.71949045693645</v>
+        <v>-12.02089282222818</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-11.68511230458112</v>
+        <v>-11.9627260848637</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-15.74162679425837</v>
+        <v>-15.96148761503092</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-14.60680023494094</v>
+        <v>-14.81154185211465</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.091768762487142</v>
+        <v>1.061199110378432</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5347847015216445</v>
+        <v>-0.5209657818136222</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.828831545768551</v>
+        <v>-1.808455469786111</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-5.295366743016189</v>
+        <v>-5.250000000000206</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.838622476390924</v>
+        <v>-1.274963426666012</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3.956772023271157</v>
+        <v>3.462107806438226</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.77290056940172</v>
+        <v>4.294308860070117</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.692776066877236</v>
+        <v>-5.100095328884457</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.955685894074705</v>
+        <v>-3.351353652306962</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.59741381352665</v>
+        <v>1.181960624020704</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.210890948337358</v>
+        <v>-2.593608394943757</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.176512795982035</v>
+        <v>-2.535441657578865</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.695762748394124</v>
+        <v>-2.037742441285751</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.232675604534904</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-7.413586566768238</v>
+        <v>-7.369035294667661</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-9.041694350667569</v>
+        <v>-8.955315837129106</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-4.084701535766648</v>
+        <v>-4.044549022251346</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.062139654661188</v>
+        <v>-3.029709228824075</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.494270095570407</v>
+        <v>-4.403914121988784</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.194639840490566</v>
+        <v>-4.131128603169657</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.06564532356478</v>
+        <v>1.117949820879019</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.267697628649394</v>
+        <v>3.306984317132844</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.311667344020037</v>
+        <v>2.385055955783656</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.1897561558687926</v>
+        <v>-0.2086841294559036</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>6.2350549976086</v>
+        <v>5.781865688494527</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>5.376576007106983</v>
+        <v>4.955076673647227</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>5.849282296650514</v>
+        <v>5.444874499295992</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.503589375448676</v>
+        <v>2.154096352461806</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>114</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.353058262372933</v>
+        <v>-2.980688283542257</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.048231870863049</v>
+        <v>2.431741679476318</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.728154308927969</v>
+        <v>-2.732640933445253</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.03074032457012521</v>
+        <v>0.02882205513804337</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.383487261245953</v>
+        <v>-1.33762006827002</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.6660836057355368</v>
+        <v>0.689551415460997</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.170502818971769</v>
+        <v>-1.125490638676752</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.7619015578354933</v>
+        <v>-0.7141304166041493</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.333132065345005</v>
+        <v>-4.25987495556511</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.428664896762392</v>
+        <v>-3.329317571468017</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-8.019330967303283</v>
+        <v>-7.919422931284807</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-7.107759832492022</v>
+        <v>-6.984063211463777</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.502028155571658</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-4.670596088210466</v>
+        <v>-4.498597328644202</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-7.253028833878744</v>
+        <v>-7.205927587702519</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.987435362215372</v>
+        <v>-1.956536773290509</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.381778209422549</v>
+        <v>-2.350274761605398</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3353279171521208</v>
+        <v>0.3437118437116453</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-4.513858557524109</v>
+        <v>-4.419041570744547</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-7.659373954503621</v>
+        <v>-7.565059470728848</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-7.750083839438162</v>
+        <v>-7.625715559954308</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-8.59150075487608</v>
+        <v>-8.946249175038304</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-7.796531944352871</v>
+        <v>-8.128520929474448</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-8.646450740682731</v>
+        <v>-8.952349510289622</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-7.127013967908447</v>
+        <v>-7.44708824842381</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-9.678842712104846</v>
+        <v>-9.95302407516148</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-7.512786668866532</v>
+        <v>-7.784079437622744</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-8.149119984157238</v>
+        <v>-8.389735430308029</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>130</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.672064260604003</v>
+        <v>3.991678099150597</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.088185253167197</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.1295633725988452</v>
+        <v>0.1283577170270718</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.797028258894329</v>
+        <v>1.796703296703207</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.796674781027207</v>
+        <v>2.845915694212906</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.518645282989254</v>
+        <v>-1.496683402352772</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.371627347348344</v>
+        <v>-2.326570260808914</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.300620649402624</v>
+        <v>-1.253941482730809</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-5.210325047801149</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-6.060243844131094</v>
+        <v>-5.960896518836257</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.95725269469898</v>
+        <v>-3.857344658680212</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-5.461336080805111</v>
+        <v>-5.337639459776959</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-7.963443591584294</v>
+        <v>-7.791444832017632</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>133</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>9.168529672689132</v>
+        <v>9.144023513458798</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>8.310235740291866</v>
+        <v>8.312726127551151</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>7.16380007361149</v>
+        <v>7.167108439988318</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.785349262973384</v>
+        <v>2.78571428571437</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.496091225905893</v>
+        <v>1.544585445514244</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.047680444780397</v>
+        <v>4.073010062077529</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.96358402488454</v>
+        <v>4.01235397285199</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.994332837406226</v>
+        <v>2.042761813972483</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.940050892048475</v>
+        <v>5.013308001828172</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>8.601410291207429</v>
+        <v>8.700757616501903</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.892949734450902</v>
+        <v>6.992857770469662</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>8.431087285302461</v>
+        <v>8.554783906330805</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.755297334244702</v>
+        <v>5.903986882022437</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.229153285223106</v>
+        <v>5.401152044789768</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>124</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.77478114639365</v>
+        <v>4.747952691242055</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>8.806396840728027</v>
+        <v>8.809936896408779</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.382010567598989</v>
+        <v>4.383940843577946</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.129011358907071</v>
+        <v>-1.131336405529964</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.666766477929606</v>
+        <v>-1.620585546481884</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.175305708986301</v>
+        <v>-2.15425164056618</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-5.482745997619851</v>
+        <v>-5.44071418140463</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-8.366631310082475</v>
+        <v>-8.32590178049756</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-7.629679886510822</v>
+        <v>-7.55642277673104</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-3.640889005421336</v>
+        <v>-3.541541680126763</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-3.039138550778198</v>
+        <v>-2.939230514759799</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-3.811212011326205</v>
+        <v>-3.68751539029796</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-4.231362864639614</v>
+        <v>-4.082673316861694</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.586272375703302</v>
+        <v>-1.41427361613674</v>
       </c>
     </row>
     <row r="28">
@@ -1716,49 +1716,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.02841882169025922</v>
+        <v>0.007873786623804335</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.3004890626137</v>
+        <v>1.302394543194573</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-3.441581016316775</v>
+        <v>-3.407890207710054</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-5.486851094549912</v>
+        <v>-5.436279547790342</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.21543484335708</v>
+        <v>1.268715915574276</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.7881711918327383</v>
+        <v>0.8220769739615577</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.6934403697266873</v>
+        <v>0.7614208847361752</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.508286418059356</v>
+        <v>-0.4238363360788213</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.1378612796852821</v>
+        <v>-0.4608089452158595</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.9877800760150635</v>
+        <v>-1.284637526030679</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-3.366394277753521</v>
+        <v>-3.647051354861652</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.158103081919933</v>
+        <v>-1.430611236201877</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.04493447056376</v>
+        <v>1.771353139392573</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.09675707731194905</v>
+        <v>-0.1378753798870349</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>145</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.06712292708607492</v>
+        <v>-0.09631872143870623</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.528587531574225</v>
+        <v>4.527400745129569</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.6855402847502248</v>
+        <v>0.6853868947459034</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.50542060075238</v>
+        <v>1.504926108374377</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.101834469584773</v>
+        <v>-1.053288549819001</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.1148052675358926</v>
+        <v>-0.09084785858627953</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.248760235267071</v>
+        <v>3.296771914257391</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.161001936307755</v>
+        <v>4.210249498701472</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>6.168985297026595</v>
+        <v>6.242242406806291</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>4.629411328282785</v>
+        <v>4.728758653577358</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>6.493675687263973</v>
+        <v>6.593583723282649</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.838398667205503</v>
+        <v>5.962095288233748</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.038937469064507</v>
+        <v>4.187627016842335</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.33363863653242</v>
+        <v>6.505637396099083</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>177</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.711174364945869</v>
+        <v>5.681978570593238</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.535016520469583</v>
+        <v>3.533829734024927</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.010301632889721</v>
+        <v>2.0101482428854</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.965385533540221</v>
+        <v>4.964891041162218</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>8.94686999174403</v>
+        <v>8.995415911509802</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.289441761492171</v>
+        <v>5.313399170441784</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.204731402225818</v>
+        <v>5.252743081216138</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.867606261264001</v>
+        <v>5.916853823657718</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.806624104741161</v>
+        <v>5.879881214520857</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.216592314061018</v>
+        <v>7.315939639355591</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>8.706806410038183</v>
+        <v>8.806714446056858</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>8.176212810981006</v>
+        <v>8.299909432009251</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.496174952018002</v>
+        <v>5.64486449979583</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>5.721910602244414</v>
+        <v>5.893909361811076</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>194</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.09640355709451853</v>
+        <v>0.06720776274188722</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.578000969185346</v>
+        <v>1.576814182740691</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.245085254533372</v>
+        <v>3.24493186452905</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.437166068224833</v>
+        <v>5.43667157584683</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>7.991660020283774</v>
+        <v>8.040205940049546</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>6.227178379815712</v>
+        <v>6.251135788765325</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>7.688859773126921</v>
+        <v>7.736871452117242</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.221791129340183</v>
+        <v>7.271038691733899</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>9.222664642920506</v>
+        <v>9.295921752700202</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.372745846590661</v>
+        <v>8.472093171885234</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9.714436440907761</v>
+        <v>9.814344476926436</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>10.7797424283147</v>
+        <v>10.90343904934294</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>9.844127657475397</v>
+        <v>9.992817205253225</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>6.461615885021608</v>
+        <v>6.63361464458827</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>210</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.757179207560888</v>
+        <v>2.727983413208257</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-2.663530695026758</v>
+        <v>-2.664717481471413</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.2750312535515462</v>
+        <v>0.2748778635472249</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.499505507621997</v>
+        <v>-1.5</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-3.466366489289129</v>
+        <v>-3.417820569523357</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.26423055489213</v>
+        <v>-1.240273145942517</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.5558209906036069</v>
+        <v>0.6038326695939276</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.3874381293736064</v>
+        <v>-0.3381905669798897</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.408722571246443</v>
+        <v>2.481979681026139</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>3.93975615586902</v>
+        <v>4.039103481163593</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.687435949989755</v>
+        <v>4.78734398600843</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.769433149964122</v>
+        <v>3.893129770992367</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>7.158806106174517</v>
+        <v>7.307495653952344</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>7.860732232591552</v>
+        <v>8.032730992158214</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>223</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.779173655564314</v>
+        <v>1.749977861211683</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.100722988509425</v>
+        <v>5.099536202064769</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.360660123933776</v>
+        <v>3.360506733929455</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2.145593787701493</v>
+        <v>2.14509929532349</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.531709218308997</v>
+        <v>-1.483163298543225</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.007817277693825</v>
+        <v>1.031774686643438</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.716828891521821</v>
+        <v>2.764840570512142</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>6.285634687196961</v>
+        <v>6.334882249590677</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>9.363665983589016</v>
+        <v>9.436923093368712</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>9.41060817380621</v>
+        <v>9.509955499100784</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>6.51532405590477</v>
+        <v>6.615232091923446</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.89499368808071</v>
+        <v>8.018690309108955</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>6.577981848220226</v>
+        <v>6.726671395998054</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.803717498446758</v>
+        <v>6.975716258013421</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>202</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-6.936361575088824</v>
+        <v>-6.965557369441456</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-3.10200311369718</v>
+        <v>-3.103189900141835</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-2.506675488551238</v>
+        <v>-2.506828878555559</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.5938466847401074</v>
+        <v>0.5933521923621043</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.4394923733060807</v>
+        <v>-0.3909464535403089</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.6371678486215018</v>
+        <v>-0.6132104396718887</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.258319811914312</v>
+        <v>1.306331490904633</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>2.771449187929541</v>
+        <v>2.820696750323258</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.2352195066543032</v>
+        <v>0.3084766164339996</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.375399720225424</v>
+        <v>0.4747470455199974</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.645946086717707</v>
+        <v>2.745854122736382</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>3.670423248974018</v>
+        <v>3.794119870002262</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>3.250272395660609</v>
+        <v>3.398961943438437</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>3.476008045887141</v>
+        <v>3.648006805453804</v>
       </c>
     </row>
   </sheetData>
@@ -2210,261 +2210,261 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 3.229</t>
+          <t>X &gt; 3.236</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4082</v>
+        <v>4093</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.002283551901868464</v>
+        <v>-0.001587713829998449</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.109168027842955</v>
+        <v>0.1089035381910293</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.02082255810170608</v>
+        <v>0.02077037259761738</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1154923976984819</v>
+        <v>0.115194457017509</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.177171590817025</v>
+        <v>0.1755485187262877</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1946121508943364</v>
+        <v>0.1935234890245567</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.2700368310116659</v>
+        <v>0.2681764558889341</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.2811854844554844</v>
+        <v>0.2792654908274628</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.3316372717486402</v>
+        <v>0.3290130771078807</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.253999915046677</v>
+        <v>0.2509658194598785</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.3078824149894572</v>
+        <v>0.3046895961274743</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3316270774861678</v>
+        <v>0.3278062056688</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2927062496264696</v>
+        <v>0.2883968566415405</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.3119116264460828</v>
+        <v>0.3069971608783106</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 6.526</t>
+          <t>X &gt; 6.534</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3998</v>
+        <v>4008</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2994151579339999</v>
+        <v>-0.3210570985188284</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2018278093837225</v>
+        <v>-0.1992854265892348</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2588864791688863</v>
+        <v>-0.2560662214038345</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1151313986969953</v>
+        <v>-0.1126818165653205</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.09084508032623972</v>
+        <v>-0.09041590247724685</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.0294161098929635</v>
+        <v>-0.01683357090931992</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.02434248159701013</v>
+        <v>0.03572497819855869</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.02048727855179777</v>
+        <v>0.03194253857922291</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.07321229918860439</v>
+        <v>0.08346532886118041</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.06169518635375226</v>
+        <v>0.04608254397513178</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.09596477016565075</v>
+        <v>0.08028838890047751</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.2444331499641166</v>
+        <v>0.2272943595210464</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2385046022271027</v>
+        <v>0.2203465014502441</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.3033821289682876</v>
+        <v>0.3088929539489058</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 9.824</t>
+          <t>X &gt; 9.831</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3896</v>
+        <v>3907</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.4983117839239668</v>
+        <v>-0.5070498192733055</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.2282331369042154</v>
+        <v>-0.2392817635395232</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2764819035413382</v>
+        <v>-0.2873843147476336</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3115894809962967</v>
+        <v>-0.3224135415146705</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2982669831614544</v>
+        <v>-0.3125478090781826</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2430556915041606</v>
+        <v>-0.244104563567042</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2369757591493382</v>
+        <v>-0.2397812194977362</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.177533562728911</v>
+        <v>-0.1805962233390375</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.2244239967885875</v>
+        <v>-0.229092477898746</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.06024384413100137</v>
+        <v>-0.06726317698012707</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.04540152970589162</v>
+        <v>-0.05250499706306044</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.02905346807597198</v>
+        <v>0.0200164427754288</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.03391149860093634</v>
+        <v>0.02304861003754866</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.06885778260620157</v>
+        <v>0.05620534222583728</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 13.12</t>
+          <t>X &gt; 13.13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3771</v>
+        <v>3782</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.6838758614011624</v>
+        <v>-0.6914507811336819</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.3781185127073527</v>
+        <v>-0.389096977535587</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.4942769985700366</v>
+        <v>-0.5049593878090164</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.4820120251721605</v>
+        <v>-0.4927271356973364</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4240384469610845</v>
+        <v>-0.4400595442689266</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.4033326101095653</v>
+        <v>-0.4047410439196497</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3413531252047122</v>
+        <v>-0.3455320327399036</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.211561583362041</v>
+        <v>-0.2162516118835995</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.2844775901740277</v>
+        <v>-0.2915437764159563</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.1662041090316748</v>
+        <v>-0.1764274221644868</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1706153786498135</v>
+        <v>-0.1808890139286703</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.04185760010213357</v>
+        <v>-0.05507318883849877</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.02293403420824802</v>
+        <v>-0.03890365120984285</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.005672945551339126</v>
+        <v>-0.01289868223932444</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 16.42</t>
+          <t>X &gt; 16.43</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3624</v>
+        <v>3635</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.6249908174466441</v>
+        <v>-0.6450542275199993</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.4067335867444939</v>
+        <v>-0.4033026274639653</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.7592256404027395</v>
+        <v>-0.7823068105419608</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.5316621237081733</v>
+        <v>-0.5553311634837854</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.4220504969962491</v>
+        <v>-0.4532014434544749</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.137211465317975</v>
+        <v>-0.1529584836690461</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.09676061488353582</v>
+        <v>-0.116273005194536</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.05726867896955667</v>
+        <v>0.049588823820649</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.0711682552963282</v>
+        <v>-0.08212288307639426</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.05883002576976537</v>
+        <v>0.04350029347463646</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1453114078652078</v>
+        <v>0.1296304332976277</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.1125109216133211</v>
+        <v>0.09329474212241706</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1492822966507106</v>
+        <v>0.1261346607101643</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.2251283221531892</v>
+        <v>0.2256962112582173</v>
       </c>
     </row>
     <row r="11">
@@ -2474,205 +2474,205 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3504</v>
+        <v>3514</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.6469666418508098</v>
+        <v>-0.66561693271899</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3378359119940839</v>
+        <v>-0.3322897615898128</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.6888649735025822</v>
+        <v>-0.6823704531559471</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.4579574142810827</v>
+        <v>-0.4804032945186094</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4400560505107052</v>
+        <v>-0.4429829071856872</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.07022903628924837</v>
+        <v>-0.08497011563948575</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.003000602978325162</v>
+        <v>-0.01647342385794559</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1498024078669289</v>
+        <v>0.1428714230334975</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.009413107077300253</v>
+        <v>-0.02052444740177606</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.04009823112555466</v>
+        <v>0.02431815275867422</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.1080233466250462</v>
+        <v>0.1045109437781733</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.1584804973685721</v>
+        <v>0.1502401236658599</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.06825519251376733</v>
+        <v>0.05558208624930927</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.08186726194574589</v>
+        <v>0.0930611002970636</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 23.01</t>
+          <t>X &gt; 23.02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3364</v>
+        <v>3375</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.6597730041795984</v>
+        <v>-0.6626391674823111</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.06366610464083067</v>
+        <v>-0.07199973204165389</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.5609475824272963</v>
+        <v>-0.568068010454553</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.4740164738342116</v>
+        <v>-0.5109890109890145</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.4626817660668934</v>
+        <v>-0.4811951943066717</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.06019734018275358</v>
+        <v>-0.1196260116818877</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.07892420993939453</v>
+        <v>0.01345797619969602</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2512505805317176</v>
+        <v>0.1988981583859228</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.3254422421958765</v>
+        <v>0.2803388115344987</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.3233666071754016</v>
+        <v>0.2854030667171514</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.462111724665526</v>
+        <v>0.4365024060371923</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3350897156206827</v>
+        <v>0.3041454653956848</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.377514094570472</v>
+        <v>0.3403889060399123</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.3229370907535838</v>
+        <v>0.3099796694068644</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 26.31</t>
+          <t>X &gt; 26.32</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3243</v>
+        <v>3254</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.4538890035073209</v>
+        <v>-0.4242222543348362</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.009280364881085745</v>
+        <v>0.0337439221142688</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4610591260545078</v>
+        <v>-0.4661551979278329</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3142259854227092</v>
+        <v>-0.3503881749199564</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2516414848962256</v>
+        <v>-0.2702249219276993</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.2470992923343616</v>
+        <v>0.1868357811664154</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.425418060200677</v>
+        <v>0.3718799376411965</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.5293274688324345</v>
+        <v>0.4588727300834066</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.454699582740723</v>
+        <v>0.3911875902340824</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.5150564330479241</v>
+        <v>0.4580224000824771</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.543434541663018</v>
+        <v>0.4995821982466424</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.4720525644479423</v>
+        <v>0.4348988127614106</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5934253299429386</v>
+        <v>0.5486630886681709</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.5284561214070038</v>
+        <v>0.5079263561058553</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 29.61</t>
+          <t>X &gt; 29.62</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3115</v>
+        <v>3124</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.2249160305343523</v>
+        <v>-0.2083215435570622</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2118978764018138</v>
+        <v>0.2399378248468338</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.1975009091214659</v>
+        <v>-0.2003986194068119</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.1779740131798491</v>
+        <v>-0.2131428571428557</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2504792375274363</v>
+        <v>-0.254391998094782</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.09644444243777883</v>
+        <v>0.0503935207241426</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.4459308807134974</v>
+        <v>0.4057374314986859</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.6698299205202858</v>
+        <v>0.6119046711153402</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.5305344775356033</v>
+        <v>0.4789320619785471</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.7251267044734249</v>
+        <v>0.6791034811635654</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.7312039064663125</v>
+        <v>0.6669630336274821</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.6233657342337864</v>
+        <v>0.5651297709923639</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.5563448969717371</v>
+        <v>0.5219718444285348</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.3647450736830251</v>
+        <v>0.3731370649586268</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2987</v>
+        <v>2996</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.2286637782821046</v>
+        <v>-0.2101118248869795</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2288855307228062</v>
+        <v>0.258161573451666</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.0191345023276881</v>
+        <v>0.01597510297668236</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2664981143474989</v>
+        <v>-0.303088803088805</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.3525197481878735</v>
+        <v>-0.3585708436069552</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.2303679527367777</v>
+        <v>0.181148275478904</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.4647845760377791</v>
+        <v>0.4207924865537436</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.8185608198550298</v>
+        <v>0.7557605269711942</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.8431866578844733</v>
+        <v>0.7855213179011429</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.01570128802021</v>
+        <v>0.962693738087161</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.963970660259406</v>
+        <v>0.8920200906845324</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.9505513287388183</v>
+        <v>0.883453427982694</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.7982277268482321</v>
+        <v>0.7552291016857922</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.6557009063683736</v>
+        <v>0.6562289894879711</v>
       </c>
     </row>
     <row r="16">
@@ -2734,101 +2734,101 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2856</v>
+        <v>2864</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.08452899564365879</v>
+        <v>0.1049509366192964</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.4628716983913463</v>
+        <v>0.4933870578678636</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.08743216757110162</v>
+        <v>-0.09065564922983782</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2874901391274065</v>
+        <v>-0.3257292445774098</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.003253780893395231</v>
+        <v>-0.01218606441240411</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.4531176916417152</v>
+        <v>0.4002155102529414</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.8072362420188526</v>
+        <v>0.7584075885667474</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.094098871575767</v>
+        <v>1.025559121377121</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.157764525326918</v>
+        <v>1.093298554125148</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.237621049113656</v>
+        <v>1.176974336311908</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.228052196488349</v>
+        <v>1.147353958583842</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.157388332036945</v>
+        <v>1.100808654063925</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.8422794955302635</v>
+        <v>0.8103627693849091</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.6478470785299066</v>
+        <v>0.6604245276729515</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 39.5</t>
+          <t>X &gt; 39.51</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2740</v>
+        <v>2747</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.2975099169972282</v>
+        <v>-0.2745611160538246</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.01997939023005557</v>
+        <v>0.05216563541170416</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.4279000827980752</v>
+        <v>-0.431006527313528</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5524983829665402</v>
+        <v>-0.5725722603451828</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3792787772924555</v>
+        <v>-0.3704094653436911</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1929643449257128</v>
+        <v>0.1571067667212347</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4197665688348877</v>
+        <v>0.3875714926340521</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.030022766760275</v>
+        <v>0.9770516871269876</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.135407993774351</v>
+        <v>1.085639485559334</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.254604751272126</v>
+        <v>1.207953553943774</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.18031047206135</v>
+        <v>1.112983412084539</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.105199573321784</v>
+        <v>1.061979843772576</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.9040268221981549</v>
+        <v>0.8851625285624536</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.874288019869951</v>
+        <v>0.9002748061890813</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2582</v>
+        <v>2589</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.2029237525420697</v>
+        <v>-0.1769070427813162</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2708322393361868</v>
+        <v>0.3048592381053155</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.1801913917058684</v>
+        <v>-0.1836691214374397</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.4748407170244136</v>
+        <v>-0.4961389961389955</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.1808730028682746</v>
+        <v>-0.1745773262801151</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.3309247086048401</v>
+        <v>0.2912583855890034</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.4608038654240687</v>
+        <v>0.4236524894137474</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.7887615574643689</v>
+        <v>0.7300205012311807</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.9042260357901881</v>
+        <v>0.8474880465345294</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.160042644448168</v>
+        <v>1.104740546800627</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.209880714107634</v>
+        <v>1.132260330924773</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.01188086491377</v>
+        <v>0.9587668366294295</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.9790266808490173</v>
+        <v>0.9497092961659916</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.9336546626014908</v>
+        <v>0.9505702020020408</v>
       </c>
     </row>
     <row r="19">
@@ -2890,49 +2890,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2456</v>
+        <v>2462</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.09724068891348026</v>
+        <v>0.1257357014714842</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.6785028297107942</v>
+        <v>0.7140133211944857</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.224743063539556</v>
+        <v>0.2207653094346611</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.03002913320426615</v>
+        <v>0.007453163969607601</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.2046151093641484</v>
+        <v>0.2084192077517528</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.6056881442948594</v>
+        <v>0.5624065130099822</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.9500966349809161</v>
+        <v>0.9077593559810282</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.237963862179726</v>
+        <v>1.172742673551397</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.444131606655503</v>
+        <v>1.379375423732505</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.838778957171925</v>
+        <v>1.773573639507049</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.593361186533876</v>
+        <v>1.528832298751304</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.668455951267056</v>
+        <v>1.627599929335851</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.492604772220751</v>
+        <v>1.476047362089929</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.596190585313728</v>
+        <v>1.626789249092162</v>
       </c>
     </row>
     <row r="20">
@@ -2942,101 +2942,101 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2323</v>
+        <v>2328</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5689121481598036</v>
+        <v>0.5800169304778251</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.062537051659554</v>
+        <v>1.080605465225517</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.6248103404440357</v>
+        <v>0.6246569504397144</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.4973035252695084</v>
+        <v>0.4968090328915054</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.4123246519718506</v>
+        <v>0.4371131565443989</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.7764687858931936</v>
+        <v>0.7528540018238061</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.207665563342424</v>
+        <v>1.207661830124117</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.452807646356035</v>
+        <v>1.429114293108469</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.502239496088691</v>
+        <v>1.478052336892638</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.054263258753195</v>
+        <v>2.028794202813053</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.935657666571352</v>
+        <v>1.910564408197928</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.185274734122537</v>
+        <v>2.183507777865223</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.851219446887477</v>
+        <v>1.874260504222356</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.076955097114009</v>
+        <v>2.123305366237723</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 52.69</t>
+          <t>X &gt; 52.7</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2213</v>
+        <v>2217</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.9245869013555819</v>
+        <v>0.9373870484794011</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.343170767696357</v>
+        <v>1.362076283825509</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.9032933838434403</v>
+        <v>0.9031399938391189</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.8079885319424065</v>
+        <v>0.8074940395644035</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.7458563059661643</v>
+        <v>0.7693048895912824</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.9981039818106368</v>
+        <v>0.9969844093123257</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.770794344566127</v>
+        <v>1.793342302946584</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.735532955222752</v>
+        <v>1.733463534444169</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.061581004592711</v>
+        <v>2.057338918090416</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.683542870735685</v>
+        <v>2.676902308407591</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.614404297202107</v>
+        <v>2.608079858165141</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.874720090768456</v>
+        <v>2.891776591019436</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.725694406908282</v>
+        <v>2.767254659042884</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.906242528892612</v>
+        <v>2.971193521960366</v>
       </c>
     </row>
     <row r="22">
@@ -3046,49 +3046,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2102</v>
+        <v>2105</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.9157585537886916</v>
+        <v>0.9307994233332266</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.442339681627473</v>
+        <v>1.46226664551272</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.047568296872434</v>
+        <v>1.047414906868113</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.130287502218522</v>
+        <v>1.129793009840519</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.8295276403342129</v>
+        <v>0.8780735600999847</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.841866040515626</v>
+        <v>0.865823449465239</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.6122625696105</v>
+        <v>1.660274248600821</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.074991709482077</v>
+        <v>2.097054314820802</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.326527068223577</v>
+        <v>2.345117335137694</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.740897925612096</v>
+        <v>2.756443148621997</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.86921294242326</v>
+        <v>2.884844268781862</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.141459791258129</v>
+        <v>3.180540697358161</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.959177634424258</v>
+        <v>3.022912462005735</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.994618327467158</v>
+        <v>3.081933571051984</v>
       </c>
     </row>
     <row r="23">
@@ -3098,49 +3098,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.384545816855208</v>
+        <v>1.401623380729866</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.03239586836969</v>
+        <v>2.053223884738898</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.336419664337541</v>
+        <v>1.336266274333219</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.366243201500204</v>
+        <v>1.365748709122201</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.129158467681613</v>
+        <v>1.177704387447385</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.125327678039596</v>
+        <v>1.14928508698921</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.643026957327642</v>
+        <v>1.691038636317963</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.007864542172157</v>
+        <v>2.028418727340245</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.327363394409907</v>
+        <v>2.342851740693412</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.884479773959448</v>
+        <v>2.924645649838261</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.679778615699256</v>
+        <v>2.720505202302171</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.015664305743016</v>
+        <v>3.079876758944174</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.796518477555239</v>
+        <v>2.885522045231745</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.022254127781771</v>
+        <v>3.134566907247113</v>
       </c>
     </row>
     <row r="24">
@@ -3150,49 +3150,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.672438602053504</v>
+        <v>1.667642299647341</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.031433552653155</v>
+        <v>2.030246766208499</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.583414031582883</v>
+        <v>1.583260641578562</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.447398493595095</v>
+        <v>1.446904001217092</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.281845894706002</v>
+        <v>1.330391814471774</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.153234833819262</v>
+        <v>1.177192242768875</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.813998382966297</v>
+        <v>1.862010061956617</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.17617655464597</v>
+        <v>2.194899346301717</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.732105655823588</v>
+        <v>2.743656236632432</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.268114364824214</v>
+        <v>3.304279200013404</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.329937726819885</v>
+        <v>3.366379434053457</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.630840399431072</v>
+        <v>3.690786852994499</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.370604258271179</v>
+        <v>3.455373335376358</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.48973010039537</v>
+        <v>3.597921924761273</v>
       </c>
     </row>
     <row r="25">
@@ -3202,49 +3202,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.260708046694496</v>
+        <v>2.257198050254907</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.296313549314938</v>
+        <v>2.295126762870282</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.844756247467338</v>
+        <v>1.844602857463016</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.520694054315207</v>
+        <v>1.520199561937204</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.663835506330251</v>
+        <v>1.712381426096023</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.734065867595092</v>
+        <v>1.758023276544705</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.444358347624778</v>
+        <v>2.492370026615099</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.885864377319017</v>
+        <v>2.935111939712733</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.426038588562484</v>
+        <v>3.465998501501545</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.053392519505358</v>
+        <v>4.118603765093155</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.019145906699706</v>
+        <v>4.084821068834742</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.508069513600489</v>
+        <v>4.597275142940127</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.08791866028708</v>
+        <v>4.202117216376301</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.256836128695426</v>
+        <v>4.394376161299107</v>
       </c>
     </row>
     <row r="26">
@@ -3254,49 +3254,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.148145894664907</v>
+        <v>2.118950100312276</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.805506705341124</v>
+        <v>2.804319918896468</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.981550771229855</v>
+        <v>1.981397381225534</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.498655130023621</v>
+        <v>1.498160637645618</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.573486361722523</v>
+        <v>1.622032281488295</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.993484548316538</v>
+        <v>2.017441957266151</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.828455366242267</v>
+        <v>2.876467045232587</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.219755821167979</v>
+        <v>3.269003383561696</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.114828326431983</v>
+        <v>4.151711951616804</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.860001554642004</v>
+        <v>4.921997411267796</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.655300396381811</v>
+        <v>4.717856963731705</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.303175481252467</v>
+        <v>5.389144485891208</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.944374321190594</v>
+        <v>5.055298637806835</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.231459664668655</v>
+        <v>5.365655578301663</v>
       </c>
     </row>
     <row r="27">
@@ -3306,49 +3306,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.524424423404234</v>
+        <v>1.495228629051603</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.316442602703553</v>
+        <v>2.315255816258897</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.52113717255466</v>
+        <v>1.520983782550339</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.384339619213783</v>
+        <v>1.38384512683578</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.580362482673493</v>
+        <v>1.628908402439265</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.810980838076269</v>
+        <v>1.834938247025882</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.727605592294751</v>
+        <v>2.775617271285071</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.328627736224966</v>
+        <v>3.377875298618683</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.041511959546881</v>
+        <v>4.075215106037291</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.527598507238395</v>
+        <v>4.586500009868509</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.456497883380351</v>
+        <v>4.515870910797027</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.025278173344219</v>
+        <v>5.108083042020404</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.872328388835079</v>
+        <v>4.979947812385824</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.231664573463753</v>
+        <v>5.362504022865799</v>
       </c>
     </row>
     <row r="28">
@@ -3358,49 +3358,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.230874362478751</v>
+        <v>1.20167856812612</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.730314179167465</v>
+        <v>1.729127392722809</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.262762590627858</v>
+        <v>1.262609200623537</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.61132834556993</v>
+        <v>1.610833853191927</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.873621034104509</v>
+        <v>1.922166953870281</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.170995063739596</v>
+        <v>2.194952472689209</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.469108576380279</v>
+        <v>3.5171202553706</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.384863804500377</v>
+        <v>4.434111366894093</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.095574442366363</v>
+        <v>5.124940795602996</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.265320613261558</v>
+        <v>5.320035067772011</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.133452666946013</v>
+        <v>5.188674824020495</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.823329726803159</v>
+        <v>5.901863395446519</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>5.694511721268334</v>
+        <v>5.797826284020971</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.847414159550219</v>
+        <v>5.974090942251763</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>1235</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.365237815619494</v>
+        <v>1.336042021266863</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.778343220531376</v>
+        <v>1.77715643408672</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.788430135371478</v>
+        <v>1.788276745367156</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.40448523847401</v>
+        <v>2.403990746096007</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.947167345297338</v>
+        <v>1.99571326506311</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.325513034851454</v>
+        <v>2.349470443801067</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.779264214046833</v>
+        <v>3.827275893037154</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.93162876864065</v>
+        <v>4.980876331034366</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.680363211308169</v>
+        <v>5.753620321087865</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.964047653844695</v>
+        <v>6.063394979139268</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>6.08323313526062</v>
+        <v>6.183141171279296</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.603441247130114</v>
+        <v>6.727137868158358</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>6.102318733897683</v>
+        <v>6.25100828167551</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.489997703962267</v>
+        <v>6.661996463528929</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>1090</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.555781217172068</v>
+        <v>1.526585422819437</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.412485032365119</v>
+        <v>1.411298245920463</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.935144840270631</v>
+        <v>1.93499145026631</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.524085580189272</v>
+        <v>2.523591087811269</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.352768504157801</v>
+        <v>2.401314423923573</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.650142533792888</v>
+        <v>2.674099942742501</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.84983584425148</v>
+        <v>3.897847523241801</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.034143347253739</v>
+        <v>5.083390909647456</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.615363025593339</v>
+        <v>5.688620135373036</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.14159101825431</v>
+        <v>6.240938343548883</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>6.028632979260173</v>
+        <v>6.128541015278849</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.70521296647788</v>
+        <v>6.828909587506125</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>6.376805232430527</v>
+        <v>6.525494780208355</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>6.510797763391004</v>
+        <v>6.682796522957666</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>913</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.7501902126200832</v>
+        <v>0.7209944182674519</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.000997547814748</v>
+        <v>0.9998107613700924</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.920574465359813</v>
+        <v>1.920421075355492</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.050799608948175</v>
+        <v>2.050305116570172</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.074393955085775</v>
+        <v>1.122939874851546</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.13847116106259</v>
+        <v>2.162428570012203</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.587167154479886</v>
+        <v>3.635178833470206</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.872562913759964</v>
+        <v>4.921810476153681</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.578283933578916</v>
+        <v>5.651541043358613</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5.933184414357498</v>
+        <v>6.032531739652072</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.509425205713946</v>
+        <v>5.609333241732621</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.420035559602681</v>
+        <v>6.543732180630926</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>6.547529832247641</v>
+        <v>6.696219380025468</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>6.663736457282511</v>
+        <v>6.835735216849173</v>
       </c>
     </row>
     <row r="32">
@@ -3569,98 +3569,98 @@
         <v>719</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.9265944006200257</v>
+        <v>0.8973986062673944</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.8453109501153122</v>
+        <v>0.8441241636706565</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.563196032675989</v>
+        <v>1.563042642671668</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.137092942606486</v>
+        <v>1.136598450228483</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.7920171946338499</v>
+        <v>-0.7434712748680781</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.035259477560345</v>
+        <v>1.059216886509958</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.480451760853285</v>
+        <v>2.528463439843605</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.238696051697978</v>
+        <v>4.287943614091695</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.594960070418601</v>
+        <v>4.668217180198297</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.274943916647857</v>
+        <v>5.37429124194243</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.374832466315333</v>
+        <v>4.474740502334008</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.243702969157447</v>
+        <v>5.367399590185691</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.658044466330821</v>
+        <v>5.806734014108649</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>6.718272467044152</v>
+        <v>6.890271226610814</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 92.27</t>
+          <t>X &gt; 92.26</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>509</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1713433014892232</v>
+        <v>0.1421475071365919</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.292966638680795</v>
+        <v>2.291779852236139</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.094658908149725</v>
+        <v>2.094505518145404</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2.224884051738087</v>
+        <v>2.224389559360084</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.3113489190746179</v>
+        <v>0.3598948388403898</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.983968528277479</v>
+        <v>2.007925937227093</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>3.274503748579093</v>
+        <v>3.322515427569414</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>6.147317226599817</v>
+        <v>6.196564788993534</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.496944107405142</v>
+        <v>5.570201217184838</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.825807236419088</v>
+        <v>5.925154561713661</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>4.245860498591121</v>
+        <v>4.345768534609796</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>5.851947884738188</v>
+        <v>5.975644505766432</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.038869722976841</v>
+        <v>5.187559270754669</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.246923644323218</v>
+        <v>6.41892240388988</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>286</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.08231463193296</v>
+        <v>-1.111510426285591</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1037020722060191</v>
+        <v>0.1025152857613634</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.107532086052373</v>
+        <v>1.107378696048052</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2.286708278591789</v>
+        <v>2.286213786213786</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.748418725496094</v>
+        <v>1.796964645261866</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.745093454431881</v>
+        <v>2.769050863381494</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.70933414411676</v>
+        <v>3.75734582310708</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.039468297532814</v>
+        <v>6.088715859926531</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.481982644506537</v>
+        <v>2.555239754286234</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3.030665246778085</v>
+        <v>3.130012572072658</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.476313738867539</v>
+        <v>2.576221774886214</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.258943639474609</v>
+        <v>4.382640260502853</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>3.8387927861612</v>
+        <v>3.987482333939028</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>5.812780184639486</v>
+        <v>5.984778944206148</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>12.99527444565613</v>
+        <v>12.9660786513035</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>7.812659781163724</v>
+        <v>7.811472994719068</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>9.798840777361072</v>
+        <v>9.79868738735675</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>6.35763734952085</v>
+        <v>6.357142857142847</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>7.009823986901353</v>
+        <v>7.058369906667124</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>10.87862658796502</v>
+        <v>10.90258399691463</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>9.603440038222658</v>
+        <v>9.651451717212979</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>13.89827615634068</v>
+        <v>13.9475237187344</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.884913047436946</v>
+        <v>7.958170157216642</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>9.415946632059473</v>
+        <v>9.515293957354046</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>2.068388330942135</v>
+        <v>2.16829636696081</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>5.674195054726027</v>
+        <v>5.797891675754272</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>5.254044201412619</v>
+        <v>5.402733749190446</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>11.43216080402011</v>
+        <v>11.60415956358677</v>
       </c>
     </row>
   </sheetData>
@@ -3904,261 +3904,261 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 3.229</t>
+          <t>X &lt; 3.236</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.090512540894217</v>
+        <v>1.061316746541586</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.6698026383065852</v>
+        <v>0.6686158518619294</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.655983634503919</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.7852197933362888</v>
+        <v>-0.7857142857142918</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-3.704461727384363</v>
+        <v>-3.655915807618591</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-3.407087697749276</v>
+        <v>-3.383130288799663</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-5.872750437967824</v>
+        <v>-5.824738758977503</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-7.530295272230759</v>
+        <v>-7.481047709837043</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-8.781753619229718</v>
+        <v>-8.708496509450022</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.869767653654819</v>
+        <v>-4.770420328360245</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-7.455421192867391</v>
+        <v>-7.355513156848716</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-8.611519230988264</v>
+        <v>-8.48782260996002</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-8.805934434075141</v>
+        <v>-8.633935674508479</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 6.526</t>
+          <t>X &lt; 6.534</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.638131588513261</v>
+        <v>8.078123469230661</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.812659781163724</v>
+        <v>7.671416972310105</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.01312649164678</v>
+        <v>7.865914278113046</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.167161159044667</v>
+        <v>5.054621848739494</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4.628871605948973</v>
+        <v>4.565372707787574</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.73576944510787</v>
+        <v>3.41455920119752</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.0558209906036</v>
+        <v>2.762187135640701</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.588752346816861</v>
+        <v>2.296354375257359</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1.93253209505599</v>
+        <v>1.667665789789197</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.273089489202327</v>
+        <v>2.618985137968295</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.473150235704033</v>
+        <v>1.823128714100847</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-2.063900183369213</v>
+        <v>-1.669000406522429</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.88881294144452</v>
+        <v>-1.47244235675489</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-4.044029672170367</v>
+        <v>-4.181977376396325</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 9.824</t>
+          <t>X &lt; 9.831</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>270</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7.519083969465647</v>
+        <v>7.637489651127773</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.167157135661071</v>
+        <v>5.316305185898116</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.142756121276413</v>
+        <v>5.291570887620317</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.013722005605516</v>
+        <v>6.1594623089088</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.845802822880188</v>
+        <v>6.039216857993779</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.402436111774534</v>
+        <v>5.426393520724147</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>5.68809612287874</v>
+        <v>5.736107801869061</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.480286738351261</v>
+        <v>4.529534300744977</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.530415692939592</v>
+        <v>5.603672802719288</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.199015415128244</v>
+        <v>3.298362740422817</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.994314256868051</v>
+        <v>3.094222292886727</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.917581298112275</v>
+        <v>2.041277919140519</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.867800815169225</v>
+        <v>2.016490362947053</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.9824253542846506</v>
+        <v>1.154424113851313</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 13.12</t>
+          <t>X &lt; 13.13</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>395</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.759590298579575</v>
+        <v>6.833322518547355</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.895239648553719</v>
+        <v>4.997620180866257</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.51312649164678</v>
+        <v>5.613983202652555</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.643351635235142</v>
+        <v>5.743867243867236</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.105062082139447</v>
+        <v>5.254618102915316</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.149271554812508</v>
+        <v>5.173228963762121</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.811396638584313</v>
+        <v>4.859408317574633</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.331669766949474</v>
+        <v>3.380917329343191</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.283345838274798</v>
+        <v>4.356602948054494</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.180262484982919</v>
+        <v>3.279609810277492</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.228725883684746</v>
+        <v>3.328633919703421</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.997281251229943</v>
+        <v>2.120977872258187</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.830294954878561</v>
+        <v>1.978984502656388</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.296536934219013</v>
+        <v>1.468535693785675</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 16.42</t>
+          <t>X &lt; 16.43</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>542</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.3456522351483</v>
+        <v>4.475182292760074</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.65697536717672</v>
+        <v>3.627299325251279</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.660727967661536</v>
+        <v>5.807090748701278</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.314938351102306</v>
+        <v>4.466386554621849</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.592146952988152</v>
+        <v>3.793313884258161</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.860000687420289</v>
+        <v>1.964146743560242</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.775290328154121</v>
+        <v>1.903490654334782</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.5702143042935859</v>
+        <v>0.6194618666873026</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.616243217881504</v>
+        <v>1.6895003276612</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.7663244215516443</v>
+        <v>0.8656717468462176</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1926195732545537</v>
+        <v>0.292527609273229</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.4114995706283295</v>
+        <v>0.5351961916565742</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1758505623333662</v>
+        <v>0.3245401101111938</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.5209230125323501</v>
+        <v>-0.5334260979841332</v>
       </c>
     </row>
     <row r="11">
@@ -4168,205 +4168,205 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.561380041973209</v>
+        <v>3.646044331269174</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.554423556160124</v>
+        <v>2.513317696563767</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.123398394970046</v>
+        <v>4.071531660201018</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3.045164324056891</v>
+        <v>3.150364650364644</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.960046976399269</v>
+        <v>2.961415809713031</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.142617380656709</v>
+        <v>1.215867204934668</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.906849619577855</v>
+        <v>1.004835175859583</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.01339122964694894</v>
+        <v>0.02038659882618532</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.9830284265190912</v>
+        <v>1.037630857159272</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.7373392374399899</v>
+        <v>0.8162119148985028</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.3815806773671042</v>
+        <v>0.396049006478151</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.1138440260970555</v>
+        <v>0.1525566186545078</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.6000375836597698</v>
+        <v>0.6623760676562895</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.3726010284482442</v>
+        <v>0.3081026792945849</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 23.01</t>
+          <t>X &lt; 23.02</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>802</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.880679979440714</v>
+        <v>2.880222747603725</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.895429048471641</v>
+        <v>0.9252984505519564</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.745046691148033</v>
+        <v>2.762043733612714</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.501206996831151</v>
+        <v>2.644096300230125</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.461670560942444</v>
+        <v>2.526594371174113</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.8887204010513443</v>
+        <v>1.133589550500822</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.4299452038799387</v>
+        <v>0.700725024550799</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.4111882778120375</v>
+        <v>-0.1932630307480139</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.5968587136365642</v>
+        <v>-0.4106997788174809</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.5739595548541985</v>
+        <v>-0.4191779634192514</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.152725551019628</v>
+        <v>-1.052817515000953</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.6195942814573243</v>
+        <v>-0.4958976604290797</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.7903685761672463</v>
+        <v>-0.6416790283894187</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.6893212052424573</v>
+        <v>-0.6420107249775384</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 26.31</t>
+          <t>X &lt; 26.32</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>923</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.690264901209957</v>
+        <v>1.57590968048936</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.5124482556000913</v>
+        <v>0.4228401222152272</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.959497022524353</v>
+        <v>1.964586004868274</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.548010356795274</v>
+        <v>1.664362519201219</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.334747889290043</v>
+        <v>1.390167141690164</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.3180405946176634</v>
+        <v>-0.1064374803522767</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.8361204013377872</v>
+        <v>-0.6471936029840748</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.303189045124526</v>
+        <v>-1.054787885518955</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.9308017541933467</v>
+        <v>-0.7094221496845208</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.130666379342273</v>
+        <v>-0.9338694918094035</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.227025175738973</v>
+        <v>-1.078456879792441</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.9759622996566861</v>
+        <v>-0.8522656786284415</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.396113152970095</v>
+        <v>-1.247423605192267</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.278719864607048</v>
+        <v>-1.215063466903864</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 29.61</t>
+          <t>X &lt; 29.62</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.7448904210785443</v>
+        <v>0.6913947664501165</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1509815158109049</v>
+        <v>-0.232648608724574</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.878748523935478</v>
+        <v>0.8802047400605346</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.9140069058904103</v>
+        <v>1.010088781275215</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.135451445862145</v>
+        <v>1.138527888804376</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1982575742626622</v>
+        <v>0.3320538980826342</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.7411536397043577</v>
+        <v>-0.6210425496155665</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.493122568391378</v>
+        <v>-1.31937699240072</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.9843041551135912</v>
+        <v>-0.8324321764320501</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.549322666543162</v>
+        <v>-1.415441973381895</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.564090301536496</v>
+        <v>-1.378307108552619</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.244811864280891</v>
+        <v>-1.078407230905164</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.042352684337878</v>
+        <v>-0.9464726000159018</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.5734121197259938</v>
+        <v>-0.6024609763671052</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.6493716175197903</v>
+        <v>0.599131872592011</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1547608873577033</v>
+        <v>-0.2277426915554415</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.2125337736112201</v>
+        <v>0.2188554545836396</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.0201509578431</v>
+        <v>1.105042016806721</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.243927450471375</v>
+        <v>1.251168977514979</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1521786215023511</v>
+        <v>-0.02815193382131298</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.6602590061707119</v>
+        <v>-0.5483316502199358</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.635371680440102</v>
+        <v>-1.474462951144346</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.611679831882434</v>
+        <v>-1.466181862072091</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.038228602810086</v>
+        <v>-1.906842464782379</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.904233740748523</v>
+        <v>-1.727167143887321</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.8698555883932</v>
+        <v>-1.70754704795857</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.481226177925556</v>
+        <v>-1.379250848204812</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.208697065845399</v>
+        <v>-1.214879991269889</v>
       </c>
     </row>
     <row r="16">
@@ -4428,101 +4428,101 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.1217075069422719</v>
+        <v>-0.1651799035556678</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.626755588944711</v>
+        <v>-0.6893554758522171</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4255408100016851</v>
+        <v>0.4297658399178061</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.9365732650904377</v>
+        <v>1.013507672357889</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.3221222496946652</v>
+        <v>0.3390735583018909</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.5990871174714627</v>
+        <v>-0.4826973883667662</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.293089175138249</v>
+        <v>-1.184679551063859</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.988642205825208</v>
+        <v>-1.837576360751122</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.049624362347984</v>
+        <v>-1.910036806662305</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.214089997977162</v>
+        <v>-2.085516579626713</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.190306769337127</v>
+        <v>-2.020550274357312</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.038493679304175</v>
+        <v>-1.92117768715071</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.349420983288262</v>
+        <v>-1.284967988016241</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.005134724878481</v>
+        <v>-1.035923126000874</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 39.5</t>
+          <t>X &lt; 39.51</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6287974565376189</v>
+        <v>0.5823134704570094</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.3134922819962256</v>
+        <v>0.250005044091985</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.037602016122307</v>
+        <v>1.037643011301945</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.34664064853115</v>
+        <v>1.376005162315096</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.018288114329792</v>
+        <v>0.9950544553127258</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.01393897569922586</v>
+        <v>0.05409011084245208</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.378565360157836</v>
+        <v>-0.3167138219832069</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.615403073223781</v>
+        <v>-1.511245154668629</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.746364236044677</v>
+        <v>-1.650317589346415</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.96647197569154</v>
+        <v>-1.878551787503568</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.821278102461179</v>
+        <v>-1.695763223355769</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.678746121744567</v>
+        <v>-1.599532702802186</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.289820716663939</v>
+        <v>-1.257272910816219</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.305767466867493</v>
+        <v>-1.357878398451199</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1584</v>
+        <v>1588</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.3825200928136638</v>
+        <v>0.3389802227022471</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.124847715537733</v>
+        <v>-0.1797009325851064</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4879375747701999</v>
+        <v>0.4910570089686956</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.030875264724742</v>
+        <v>1.059262903658642</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.5555976839037839</v>
+        <v>0.5420791798500844</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.2182318151315741</v>
+        <v>-0.1535437833510898</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.3659541466724718</v>
+        <v>-0.3055298206970463</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.959046735008684</v>
+        <v>-0.8628071932914381</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.08304086380619</v>
+        <v>-0.9913392948053712</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.491875854212921</v>
+        <v>-1.404014054977225</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.570553067923655</v>
+        <v>-1.448055834297058</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.249482360754669</v>
+        <v>-1.166656257956653</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.193304454137937</v>
+        <v>-1.149383319299424</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.185083063223757</v>
+        <v>-1.215199918241225</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1710</v>
+        <v>1715</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.09163864125696364</v>
+        <v>-0.1319215696665665</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.6810234063970171</v>
+        <v>-0.7290197685115203</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.1428501847380588</v>
+        <v>-0.1366788705153112</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.1941100949784271</v>
+        <v>0.2252237321842827</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.05246417223627731</v>
+        <v>-0.05823181237219899</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.5718929430679438</v>
+        <v>-0.5085658288693509</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.006661645391283</v>
+        <v>-0.9445472866884117</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.473730289178022</v>
+        <v>-1.379165096326517</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.70974161722939</v>
+        <v>-1.617579863559556</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.26794512767826</v>
+        <v>-2.17742736866181</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.915849847691845</v>
+        <v>-1.826073658277011</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.024959373400371</v>
+        <v>-1.969341091478491</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.770530678217789</v>
+        <v>-1.749841566650176</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.980537608678311</v>
+        <v>-2.025578045742684</v>
       </c>
     </row>
     <row r="20">
@@ -4636,101 +4636,101 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1843</v>
+        <v>1849</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.6710835075737904</v>
+        <v>-0.6821548356396718</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.06507509657115</v>
+        <v>-1.082536221870789</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.6199183974824791</v>
+        <v>-0.616059156422061</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.4064319145484134</v>
+        <v>-0.4034042880196722</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.2953708182934491</v>
+        <v>-0.3254016859311619</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.7014599921215705</v>
+        <v>-0.6694600064702527</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.190124815981072</v>
+        <v>-1.185986706432352</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.548909756465164</v>
+        <v>-1.515189668507297</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.555750061336617</v>
+        <v>-1.523259955281425</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.243243302712493</v>
+        <v>-2.210221937077129</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.093764070646891</v>
+        <v>-2.061365260109028</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.409428638653765</v>
+        <v>-2.406167905939014</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.986943299878575</v>
+        <v>-2.015541669084975</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.328400392786349</v>
+        <v>-2.386028182685351</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 52.69</t>
+          <t>X &lt; 52.7</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1953</v>
+        <v>1960</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.002832442359022</v>
+        <v>-1.01340964325329</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.261913444352899</v>
+        <v>-1.27745938188454</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.8644245287613757</v>
+        <v>-0.8594266954148679</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7068270273478134</v>
+        <v>-0.702320522117482</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.6325591531846939</v>
+        <v>-0.6564478640165632</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.8692697104930858</v>
+        <v>-0.8642568857799162</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.693004957762454</v>
+        <v>-1.711029218221704</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.700186018513939</v>
+        <v>-1.692160435700529</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.016661276722971</v>
+        <v>-2.007296945655042</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.713284212041081</v>
+        <v>-2.702240714355788</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.635088151675447</v>
+        <v>-2.624537730509054</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.931334113462988</v>
+        <v>-2.946829454287958</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.761260180319603</v>
+        <v>-2.804934835836626</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.019964131975797</v>
+        <v>-3.089717987433637</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2064</v>
+        <v>2072</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.8897877759538346</v>
+        <v>-0.9018545037155903</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.221865751191039</v>
+        <v>-1.236831876917535</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.9154449369246507</v>
+        <v>-0.9104546467972909</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.9524957814717609</v>
+        <v>-0.9469603403321045</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.6437301883919559</v>
+        <v>-0.6897365439861787</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.6101303454511751</v>
+        <v>-0.6312987869681663</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.345717187530312</v>
+        <v>-1.38750932174807</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.86114173073679</v>
+        <v>-1.875841238413045</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.067191585518749</v>
+        <v>-2.079773763731616</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.481907287071053</v>
+        <v>-2.492688426350888</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.612308330886606</v>
+        <v>-2.622868291673726</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.890779821962305</v>
+        <v>-2.92461371984659</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.703986468482455</v>
+        <v>-2.763484981427709</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.791261122890198</v>
+        <v>-2.874604915177713</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2176</v>
+        <v>2185</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.2234857607584</v>
+        <v>-1.23506628754636</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.62183679880404</v>
+        <v>-1.634272516600213</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.077262524371527</v>
+        <v>-1.071726351909454</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.059945068061559</v>
+        <v>-1.054181581516438</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.8408838638064964</v>
+        <v>-0.8810319251686209</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.7937142090320606</v>
+        <v>-0.8116365750350809</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.220559437771328</v>
+        <v>-1.258350159742193</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.59592702699593</v>
+        <v>-1.608538961928929</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.840311292642966</v>
+        <v>-1.849396705144741</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.344647513855783</v>
+        <v>-2.374784138754208</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.157556291973577</v>
+        <v>-2.188802962716217</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.465644903295747</v>
+        <v>-2.517478368010828</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.263946917864672</v>
+        <v>-2.339173626751702</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.518732053122754</v>
+        <v>-2.614539357629319</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2290</v>
+        <v>2299</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.329242844962863</v>
+        <v>-1.320150769066998</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.439928210554704</v>
+        <v>-1.432103276118127</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.159339798044392</v>
+        <v>-1.153693565024206</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.005908591048588</v>
+        <v>-1.000711501577683</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.8679461895192375</v>
+        <v>-0.9035843724448682</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.7212572680164087</v>
+        <v>-0.7374556340222824</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.218221959909933</v>
+        <v>-1.2517820828118</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.554571649448306</v>
+        <v>-1.56430357183477</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.964137683966733</v>
+        <v>-1.968665160243674</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.398517601759607</v>
+        <v>-2.422034165384417</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.44898338006238</v>
+        <v>-2.472595611029348</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.696535436423311</v>
+        <v>-2.738769403279683</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.482232325784906</v>
+        <v>-2.545506416441022</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.625855415568168</v>
+        <v>-2.707963719828392</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2406</v>
+        <v>2416</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.61242967817703</v>
+        <v>-1.604016272992425</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.464878292402481</v>
+        <v>-1.457374577258655</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.217005958684346</v>
+        <v>-1.211377949037384</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.9404992964418781</v>
+        <v>-0.9358732775880441</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.042410991597087</v>
+        <v>-1.07319612180612</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.054256801611288</v>
+        <v>-1.067005819209847</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.53136214135565</v>
+        <v>-1.559561784349441</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.893432480660373</v>
+        <v>-1.920904577439572</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.244750597365645</v>
+        <v>-2.266353357269701</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.6992479935086</v>
+        <v>-2.737756022968661</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.674243466484185</v>
+        <v>-2.713197363230734</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.032892431431229</v>
+        <v>-3.08784624224171</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.724668679668355</v>
+        <v>-2.79909062971295</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.892147472906629</v>
+        <v>-2.983115743887218</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2536</v>
+        <v>2546</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.342768463815361</v>
+        <v>-1.318239999955374</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.598972952023779</v>
+        <v>-1.5913342579709</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.148303201990302</v>
+        <v>-1.143264677004389</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.800656223311023</v>
+        <v>-0.7968924659065522</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.8461957794957726</v>
+        <v>-0.8737892583687525</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.078098689641116</v>
+        <v>-1.088876643723772</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.574485105084079</v>
+        <v>-1.598618228509153</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.863235059715997</v>
+        <v>-1.886929184684028</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.396472233948337</v>
+        <v>-2.412646142647084</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.871267466178253</v>
+        <v>-2.902072989424667</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.739935155994978</v>
+        <v>-2.771549324159892</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-3.15728079802642</v>
+        <v>-3.202631610483301</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.925845807409203</v>
+        <v>-2.988090189336681</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-3.152111390662185</v>
+        <v>-3.228631368968507</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2669</v>
+        <v>2679</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.8210876083038414</v>
+        <v>-0.801345108690839</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.107027496732513</v>
+        <v>-1.101835918589842</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.7354737323173879</v>
+        <v>-0.7323800582088396</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.6225184170426843</v>
+        <v>-0.6196939913935111</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.7298277198777399</v>
+        <v>-0.7541300933328756</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.8232739031731526</v>
+        <v>-0.8333757386729488</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.299096677398182</v>
+        <v>-1.320785278851275</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.671407214389816</v>
+        <v>-1.692274099834378</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.031566633440647</v>
+        <v>-2.044668534146638</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.300423417643913</v>
+        <v>-2.326904718612802</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.26045398442713</v>
+        <v>-2.287333759810259</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.580248617164294</v>
+        <v>-2.619365566568241</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.493414332562772</v>
+        <v>-2.546804274974441</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.734461258817767</v>
+        <v>-2.800202405164896</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2793</v>
+        <v>2803</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.5736076526377403</v>
+        <v>-0.5569868248869838</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.6684216671074523</v>
+        <v>-0.6652249668812047</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.5089926663981714</v>
+        <v>-0.5069273958699725</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.6450138180125364</v>
+        <v>-0.6422477273881455</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.7714106061861514</v>
+        <v>-0.7923379440407246</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.8832781739397504</v>
+        <v>-0.8916427652950674</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.484703686577028</v>
+        <v>-1.502589970636549</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.968499431664362</v>
+        <v>-1.985107788834817</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.279660287257904</v>
+        <v>-2.288065089018609</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.359850565618316</v>
+        <v>-2.380561641743455</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.29498792084614</v>
+        <v>-2.316141741853635</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.634860231073439</v>
+        <v>-2.666585024016541</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.570545906642053</v>
+        <v>-2.614724303930949</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.683485454483296</v>
+        <v>-2.738891249317774</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2931</v>
+        <v>2942</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.5447747261865246</v>
+        <v>-0.5304163934149031</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.5752825517327338</v>
+        <v>-0.5726389438952424</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.6459489672247329</v>
+        <v>-0.6434779650693656</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.87143925221811</v>
+        <v>-0.8679829655439448</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.6772508430306203</v>
+        <v>-0.6952567896908448</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.8037564707365306</v>
+        <v>-0.8108946148690777</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.380708556545414</v>
+        <v>-1.395876674978084</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.897725594717258</v>
+        <v>-1.911492886550867</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.178989897937392</v>
+        <v>-2.201879610909138</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.295337540894216</v>
+        <v>-2.328853070092379</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.345381266876551</v>
+        <v>-2.378958867900536</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.565377623987466</v>
+        <v>-2.608228924659805</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.353309790661697</v>
+        <v>-2.40756672166048</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.552583554316882</v>
+        <v>-2.616001648416734</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3076</v>
+        <v>3087</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.5223533889027507</v>
+        <v>-0.5101118248869838</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3356254396603546</v>
+        <v>-0.3340117238537417</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5834073599891099</v>
+        <v>-0.5812812560076424</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.7597591878367922</v>
+        <v>-0.7568845426449542</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.6972069616206795</v>
+        <v>-0.7120250730301763</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.7713641476288373</v>
+        <v>-0.7771605988235137</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.16297486377448</v>
+        <v>-1.175956169018441</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.612678387709266</v>
+        <v>-1.624505286854259</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.786112129917342</v>
+        <v>-1.805890706456125</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.969334753221922</v>
+        <v>-1.99777778703443</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.929121683131697</v>
+        <v>-1.957917225272197</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.169488227553749</v>
+        <v>-2.205931413857101</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.052082669225143</v>
+        <v>-2.09788307785125</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.133694666906884</v>
+        <v>-2.187547595467329</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3253</v>
+        <v>3264</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1845290127756272</v>
+        <v>-0.1756595819818898</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1257927820974203</v>
+        <v>-0.1250349417888685</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4427558612944011</v>
+        <v>-0.4412253716399874</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.4492012302260946</v>
+        <v>-0.447552142420804</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1739078749421026</v>
+        <v>-0.1870580537012643</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.4423967615772</v>
+        <v>-0.4476896088602089</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.8172435726450118</v>
+        <v>-0.8280870869971864</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.206415612972144</v>
+        <v>-1.216303279954985</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.373615409986542</v>
+        <v>-1.389744597550369</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.470130242657262</v>
+        <v>-1.49333225935051</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.350940088386288</v>
+        <v>-1.374709448772279</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.606910936057382</v>
+        <v>-1.63657016777065</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.641498281099743</v>
+        <v>-1.678138415908371</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.706260872673937</v>
+        <v>-1.749306822967853</v>
       </c>
     </row>
     <row r="32">
@@ -5260,101 +5260,101 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3447</v>
+        <v>3458</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1687773022106569</v>
+        <v>-0.1620853195571001</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.03023453180864522</v>
+        <v>-0.02988833367395927</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2358613626042327</v>
+        <v>-0.2350810926498426</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1188699441689636</v>
+        <v>-0.1183885318833404</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.2844602302875998</v>
+        <v>0.2733080307485949</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.06789673916613026</v>
+        <v>-0.07274092820833999</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.3394832804968431</v>
+        <v>-0.3485482827870285</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.7328934270443739</v>
+        <v>-0.7409729270370846</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.7781118380676588</v>
+        <v>-0.7911251138805397</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.9168071591121745</v>
+        <v>-0.9348999850409427</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.7287131183332249</v>
+        <v>-0.7475275760229181</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.9101841304069964</v>
+        <v>-0.9334598243833554</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.9952652671543873</v>
+        <v>-1.023566172339308</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.246566039197596</v>
+        <v>-1.27900989853007</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 92.27</t>
+          <t>X &lt; 92.26</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3657</v>
+        <v>3668</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.001351997836806618</v>
+        <v>0.002792277259167975</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1809546719764796</v>
+        <v>-0.1802454317819695</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2066117853434051</v>
+        <v>-0.2059722639460091</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1979355204779765</v>
+        <v>-0.1972733628524779</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.06960108923163943</v>
+        <v>0.06250112129603025</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1364451979116836</v>
+        <v>-0.1394389058264522</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.2881694439981857</v>
+        <v>-0.2941265140795437</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.7130884550239358</v>
+        <v>-0.7179505275781821</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.5953605475280739</v>
+        <v>-0.6039887112313593</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.6382280014650661</v>
+        <v>-0.6504390024965616</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.4179504668720782</v>
+        <v>-0.4309045773776958</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.6416081181419244</v>
+        <v>-0.6572789483536781</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.5271529138468338</v>
+        <v>-0.5467269835899984</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.7235874673967473</v>
+        <v>-0.7458949620402819</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3880</v>
+        <v>3891</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1006406095889432</v>
+        <v>0.1025930931457992</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1216697160729368</v>
+        <v>0.1214177258782456</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.002165207145303327</v>
+        <v>-0.002147349408282651</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.06358923880085143</v>
+        <v>-0.06337202915003104</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.02221999551547782</v>
+        <v>-0.02587917758195601</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.07081491703204534</v>
+        <v>-0.07245233718813893</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1157705171083023</v>
+        <v>-0.1191266013386709</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.3114633235995257</v>
+        <v>-0.3143627140527414</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.02370986118596363</v>
+        <v>-0.02926506327812461</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.06127371024841466</v>
+        <v>-0.06872707082617069</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.01977374305563018</v>
+        <v>-0.02738930330113476</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1512263039256183</v>
+        <v>-0.1602994609624204</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1188960079099672</v>
+        <v>-0.1299829346053727</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2909614345660501</v>
+        <v>-0.3033559484006076</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4082</v>
+        <v>4093</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.2464837961021118</v>
+        <v>-0.245133744029701</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.03738790767243216</v>
+        <v>-0.03725967739971736</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1257691838968285</v>
+        <v>-0.1254284578117293</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.03113516828392449</v>
+        <v>-0.03104000557083708</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.04282352040272031</v>
+        <v>-0.04385664948434709</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.09878638211299062</v>
+        <v>-0.09908806913198731</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.04788931229965243</v>
+        <v>-0.04889671484276903</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1591276270905055</v>
+        <v>-0.1598660046592357</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.01091227559660268</v>
+        <v>-0.01261698633770436</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.03968584119414942</v>
+        <v>-0.04193142242442605</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1120439816969281</v>
+        <v>0.1093770961274743</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.03779749864189341</v>
+        <v>0.03476591262850803</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.04778829714054922</v>
+        <v>0.04413696411589285</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1045508919272606</v>
+        <v>-0.1083461081175443</v>
       </c>
     </row>
   </sheetData>
